--- a/research/traditional_assets/database/data/canada/canada_information_services.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_information_services.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08992829127703954</v>
+        <v>0.08972305630515537</v>
       </c>
       <c r="C2">
-        <v>2456.605817849298</v>
+        <v>2434.483272503817</v>
       </c>
       <c r="D2">
-        <v>2307.605817849298</v>
+        <v>2312.289272503817</v>
       </c>
       <c r="E2">
-        <v>-1601</v>
+        <v>-1574.194</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>26.806</v>
       </c>
       <c r="G2">
         <v>149</v>
@@ -1445,28 +1445,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.3483418</v>
       </c>
       <c r="N2">
-        <v>268.6666666666667</v>
+        <v>267.3183248666667</v>
       </c>
       <c r="O2">
-        <v>71.19666666666669</v>
+        <v>70.83935608966668</v>
       </c>
       <c r="P2">
-        <v>197.4700000000001</v>
+        <v>196.478968777</v>
       </c>
       <c r="Q2">
-        <v>520.47</v>
+        <v>519.4789687770001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08992829127703954</v>
+        <v>0.09025591040924785</v>
       </c>
       <c r="T2">
-        <v>1.01912912879999</v>
+        <v>1.026695390513807</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>199.257092427652</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08972305630515537</v>
+        <v>0.08951782133327121</v>
       </c>
       <c r="C3">
-        <v>2434.483272503817</v>
+        <v>2412.379776647673</v>
       </c>
       <c r="D3">
-        <v>2312.289272503817</v>
+        <v>2316.991776647673</v>
       </c>
       <c r="E3">
-        <v>-1574.194</v>
+        <v>-1547.388</v>
       </c>
       <c r="F3">
-        <v>26.806</v>
+        <v>53.612</v>
       </c>
       <c r="G3">
         <v>149</v>
@@ -1527,28 +1527,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M3">
-        <v>1.3483418</v>
+        <v>2.6966836</v>
       </c>
       <c r="N3">
-        <v>267.3183248666667</v>
+        <v>265.9699830666667</v>
       </c>
       <c r="O3">
-        <v>70.83935608966668</v>
+        <v>70.48204551266669</v>
       </c>
       <c r="P3">
-        <v>196.478968777</v>
+        <v>195.487937554</v>
       </c>
       <c r="Q3">
-        <v>519.4789687770001</v>
+        <v>518.487937554</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09025591040924785</v>
+        <v>0.09059021564619513</v>
       </c>
       <c r="T3">
-        <v>1.026695390513807</v>
+        <v>1.034416065731989</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>199.257092427652</v>
+        <v>99.62854621382601</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08951782133327121</v>
+        <v>0.08931258636138707</v>
       </c>
       <c r="C4">
-        <v>2412.379776647673</v>
+        <v>2390.295446740585</v>
       </c>
       <c r="D4">
-        <v>2316.991776647673</v>
+        <v>2321.713446740585</v>
       </c>
       <c r="E4">
-        <v>-1547.388</v>
+        <v>-1520.582</v>
       </c>
       <c r="F4">
-        <v>53.612</v>
+        <v>80.41799999999999</v>
       </c>
       <c r="G4">
         <v>149</v>
@@ -1609,28 +1609,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M4">
-        <v>2.6966836</v>
+        <v>4.045025399999999</v>
       </c>
       <c r="N4">
-        <v>265.9699830666667</v>
+        <v>264.6216412666668</v>
       </c>
       <c r="O4">
-        <v>70.48204551266669</v>
+        <v>70.12473493566669</v>
       </c>
       <c r="P4">
-        <v>195.487937554</v>
+        <v>194.496906331</v>
       </c>
       <c r="Q4">
-        <v>518.487937554</v>
+        <v>517.496906331</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09059021564619513</v>
+        <v>0.09093141377462585</v>
       </c>
       <c r="T4">
-        <v>1.034416065731989</v>
+        <v>1.042295930129927</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>99.62854621382601</v>
+        <v>66.41903080921738</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08931258636138707</v>
+        <v>0.0891073513895029</v>
       </c>
       <c r="C5">
-        <v>2390.295446740585</v>
+        <v>2368.23040019352</v>
       </c>
       <c r="D5">
-        <v>2321.713446740585</v>
+        <v>2326.45440019352</v>
       </c>
       <c r="E5">
-        <v>-1520.582</v>
+        <v>-1493.776</v>
       </c>
       <c r="F5">
-        <v>80.41799999999999</v>
+        <v>107.224</v>
       </c>
       <c r="G5">
         <v>149</v>
@@ -1691,28 +1691,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M5">
-        <v>4.045025399999999</v>
+        <v>5.3933672</v>
       </c>
       <c r="N5">
-        <v>264.6216412666668</v>
+        <v>263.2732994666667</v>
       </c>
       <c r="O5">
-        <v>70.12473493566669</v>
+        <v>69.76742435866669</v>
       </c>
       <c r="P5">
-        <v>194.496906331</v>
+        <v>193.5058751080001</v>
       </c>
       <c r="Q5">
-        <v>517.496906331</v>
+        <v>516.5058751080001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09093141377462585</v>
+        <v>0.09127972019739886</v>
       </c>
       <c r="T5">
-        <v>1.042295930129927</v>
+        <v>1.050339958369489</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>66.41903080921738</v>
+        <v>49.81427310691301</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0891073513895029</v>
+        <v>0.08890211641761876</v>
       </c>
       <c r="C6">
-        <v>2368.23040019352</v>
+        <v>2346.18475537842</v>
       </c>
       <c r="D6">
-        <v>2326.45440019352</v>
+        <v>2331.21475537842</v>
       </c>
       <c r="E6">
-        <v>-1493.776</v>
+        <v>-1466.97</v>
       </c>
       <c r="F6">
-        <v>107.224</v>
+        <v>134.03</v>
       </c>
       <c r="G6">
         <v>149</v>
@@ -1773,28 +1773,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M6">
-        <v>5.3933672</v>
+        <v>6.741708999999999</v>
       </c>
       <c r="N6">
-        <v>263.2732994666667</v>
+        <v>261.9249576666667</v>
       </c>
       <c r="O6">
-        <v>69.76742435866669</v>
+        <v>69.41011378166668</v>
       </c>
       <c r="P6">
-        <v>193.5058751080001</v>
+        <v>192.5148438850001</v>
       </c>
       <c r="Q6">
-        <v>516.5058751080001</v>
+        <v>515.5148438850001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09127972019739886</v>
+        <v>0.09163535938696712</v>
       </c>
       <c r="T6">
-        <v>1.050339958369489</v>
+        <v>1.058553334571989</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>49.81427310691301</v>
+        <v>39.85141848553042</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08890211641761876</v>
+        <v>0.08869688144573462</v>
       </c>
       <c r="C7">
-        <v>2346.18475537842</v>
+        <v>2324.158631638058</v>
       </c>
       <c r="D7">
-        <v>2331.21475537842</v>
+        <v>2335.994631638058</v>
       </c>
       <c r="E7">
-        <v>-1466.97</v>
+        <v>-1440.164</v>
       </c>
       <c r="F7">
-        <v>134.03</v>
+        <v>160.836</v>
       </c>
       <c r="G7">
         <v>149</v>
@@ -1855,28 +1855,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M7">
-        <v>6.741708999999999</v>
+        <v>8.0900508</v>
       </c>
       <c r="N7">
-        <v>261.9249576666667</v>
+        <v>260.5766158666668</v>
       </c>
       <c r="O7">
-        <v>69.41011378166668</v>
+        <v>69.0528032046667</v>
       </c>
       <c r="P7">
-        <v>192.5148438850001</v>
+        <v>191.5238126620001</v>
       </c>
       <c r="Q7">
-        <v>515.5148438850001</v>
+        <v>514.5238126620001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09163535938696712</v>
+        <v>0.09199856536780279</v>
       </c>
       <c r="T7">
-        <v>1.058553334571989</v>
+        <v>1.066941463459649</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>39.85141848553042</v>
+        <v>33.20951540460868</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08869688144573459</v>
+        <v>0.08849164647385047</v>
       </c>
       <c r="C8">
-        <v>2324.158631638059</v>
+        <v>2302.152149296011</v>
       </c>
       <c r="D8">
-        <v>2335.994631638058</v>
+        <v>2340.794149296011</v>
       </c>
       <c r="E8">
-        <v>-1440.164</v>
+        <v>-1413.358</v>
       </c>
       <c r="F8">
-        <v>160.836</v>
+        <v>187.642</v>
       </c>
       <c r="G8">
         <v>149</v>
@@ -1937,28 +1937,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M8">
-        <v>8.090050799999998</v>
+        <v>9.438392599999998</v>
       </c>
       <c r="N8">
-        <v>260.5766158666668</v>
+        <v>259.2282740666668</v>
       </c>
       <c r="O8">
-        <v>69.0528032046667</v>
+        <v>68.6954926276667</v>
       </c>
       <c r="P8">
-        <v>191.5238126620001</v>
+        <v>190.5327814390001</v>
       </c>
       <c r="Q8">
-        <v>514.5238126620001</v>
+        <v>513.532781439</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09199856536780276</v>
+        <v>0.09236958222994673</v>
       </c>
       <c r="T8">
-        <v>1.066941463459649</v>
+        <v>1.07550998221586</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>33.20951540460869</v>
+        <v>28.46529891823601</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08849164647385045</v>
+        <v>0.08828641150196631</v>
       </c>
       <c r="C9">
-        <v>2302.152149296012</v>
+        <v>2280.165429666756</v>
       </c>
       <c r="D9">
-        <v>2340.794149296012</v>
+        <v>2345.613429666756</v>
       </c>
       <c r="E9">
-        <v>-1413.358</v>
+        <v>-1386.552</v>
       </c>
       <c r="F9">
-        <v>187.642</v>
+        <v>214.448</v>
       </c>
       <c r="G9">
         <v>149</v>
@@ -2019,28 +2019,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M9">
-        <v>9.4383926</v>
+        <v>10.7867344</v>
       </c>
       <c r="N9">
-        <v>259.2282740666668</v>
+        <v>257.8799322666667</v>
       </c>
       <c r="O9">
-        <v>68.6954926276667</v>
+        <v>68.33818205066669</v>
       </c>
       <c r="P9">
-        <v>190.5327814390001</v>
+        <v>189.5417502160001</v>
       </c>
       <c r="Q9">
-        <v>513.532781439</v>
+        <v>512.5417502160001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09236958222994673</v>
+        <v>0.09274866467605034</v>
       </c>
       <c r="T9">
-        <v>1.07550998221586</v>
+        <v>1.084264773118945</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>28.46529891823601</v>
+        <v>24.90713655345651</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08828641150196631</v>
+        <v>0.08808117653008213</v>
       </c>
       <c r="C10">
-        <v>2280.165429666756</v>
+        <v>2258.19859506589</v>
       </c>
       <c r="D10">
-        <v>2345.613429666756</v>
+        <v>2350.45259506589</v>
       </c>
       <c r="E10">
-        <v>-1386.552</v>
+        <v>-1359.746</v>
       </c>
       <c r="F10">
-        <v>214.448</v>
+        <v>241.254</v>
       </c>
       <c r="G10">
         <v>149</v>
@@ -2101,28 +2101,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M10">
-        <v>10.7867344</v>
+        <v>12.1350762</v>
       </c>
       <c r="N10">
-        <v>257.8799322666667</v>
+        <v>256.5315904666667</v>
       </c>
       <c r="O10">
-        <v>68.33818205066669</v>
+        <v>67.98087147366668</v>
       </c>
       <c r="P10">
-        <v>189.5417502160001</v>
+        <v>188.550718993</v>
       </c>
       <c r="Q10">
-        <v>512.5417502160001</v>
+        <v>511.550718993</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09274866467605034</v>
+        <v>0.09313607860448586</v>
       </c>
       <c r="T10">
-        <v>1.084264773118945</v>
+        <v>1.093211977008912</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.90713655345651</v>
+        <v>22.13967693640578</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08808117653008213</v>
+        <v>0.08787594155819797</v>
       </c>
       <c r="C11">
-        <v>2258.19859506589</v>
+        <v>2236.251768820479</v>
       </c>
       <c r="D11">
-        <v>2350.45259506589</v>
+        <v>2355.311768820479</v>
       </c>
       <c r="E11">
-        <v>-1359.746</v>
+        <v>-1332.94</v>
       </c>
       <c r="F11">
-        <v>241.254</v>
+        <v>268.0599999999999</v>
       </c>
       <c r="G11">
         <v>149</v>
@@ -2183,28 +2183,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M11">
-        <v>12.1350762</v>
+        <v>13.483418</v>
       </c>
       <c r="N11">
-        <v>256.5315904666667</v>
+        <v>255.1832486666667</v>
       </c>
       <c r="O11">
-        <v>67.98087147366668</v>
+        <v>67.62356089666669</v>
       </c>
       <c r="P11">
-        <v>188.550718993</v>
+        <v>187.55968777</v>
       </c>
       <c r="Q11">
-        <v>511.550718993</v>
+        <v>510.55968777</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09313607860448586</v>
+        <v>0.09353210173133109</v>
       </c>
       <c r="T11">
-        <v>1.093211977008912</v>
+        <v>1.102358007651989</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.13967693640578</v>
+        <v>19.92570924276521</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08787594155819797</v>
+        <v>0.08767070658631385</v>
       </c>
       <c r="C12">
-        <v>2236.251768820479</v>
+        <v>2214.325075279536</v>
       </c>
       <c r="D12">
-        <v>2355.311768820479</v>
+        <v>2360.191075279536</v>
       </c>
       <c r="E12">
-        <v>-1332.94</v>
+        <v>-1306.134</v>
       </c>
       <c r="F12">
-        <v>268.06</v>
+        <v>294.866</v>
       </c>
       <c r="G12">
         <v>149</v>
@@ -2265,28 +2265,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M12">
-        <v>13.483418</v>
+        <v>14.8317598</v>
       </c>
       <c r="N12">
-        <v>255.1832486666667</v>
+        <v>253.8349068666668</v>
       </c>
       <c r="O12">
-        <v>67.62356089666669</v>
+        <v>67.2662503196667</v>
       </c>
       <c r="P12">
-        <v>187.55968777</v>
+        <v>186.568656547</v>
       </c>
       <c r="Q12">
-        <v>510.55968777</v>
+        <v>509.568656547</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09353210173133109</v>
+        <v>0.09393702425428521</v>
       </c>
       <c r="T12">
-        <v>1.102358007651989</v>
+        <v>1.111709567073562</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.92570924276521</v>
+        <v>18.11428112978655</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08767070658631385</v>
+        <v>0.08746547161442968</v>
       </c>
       <c r="C13">
-        <v>2214.325075279536</v>
+        <v>2192.418639824629</v>
       </c>
       <c r="D13">
-        <v>2360.191075279536</v>
+        <v>2365.090639824629</v>
       </c>
       <c r="E13">
-        <v>-1306.134</v>
+        <v>-1279.328</v>
       </c>
       <c r="F13">
-        <v>294.866</v>
+        <v>321.672</v>
       </c>
       <c r="G13">
         <v>149</v>
@@ -2347,28 +2347,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M13">
-        <v>14.8317598</v>
+        <v>16.1801016</v>
       </c>
       <c r="N13">
-        <v>253.8349068666668</v>
+        <v>252.4865650666667</v>
       </c>
       <c r="O13">
-        <v>67.2662503196667</v>
+        <v>66.90893974266669</v>
       </c>
       <c r="P13">
-        <v>186.568656547</v>
+        <v>185.5776253240001</v>
       </c>
       <c r="Q13">
-        <v>509.568656547</v>
+        <v>508.5776253240001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09393702425428521</v>
+        <v>0.09435114956185189</v>
       </c>
       <c r="T13">
-        <v>1.111709567073562</v>
+        <v>1.121273661936534</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.11428112978655</v>
+        <v>16.60475770230434</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08746547161442968</v>
+        <v>0.08726023664254552</v>
       </c>
       <c r="C14">
-        <v>2192.418639824629</v>
+        <v>2170.532588880617</v>
       </c>
       <c r="D14">
-        <v>2365.090639824629</v>
+        <v>2370.010588880617</v>
       </c>
       <c r="E14">
-        <v>-1279.328</v>
+        <v>-1252.522</v>
       </c>
       <c r="F14">
-        <v>321.672</v>
+        <v>348.478</v>
       </c>
       <c r="G14">
         <v>149</v>
@@ -2429,28 +2429,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M14">
-        <v>16.1801016</v>
+        <v>17.5284434</v>
       </c>
       <c r="N14">
-        <v>252.4865650666667</v>
+        <v>251.1382232666667</v>
       </c>
       <c r="O14">
-        <v>66.90893974266669</v>
+        <v>66.55162916566668</v>
       </c>
       <c r="P14">
-        <v>185.5776253240001</v>
+        <v>184.5865941010001</v>
       </c>
       <c r="Q14">
-        <v>508.5776253240001</v>
+        <v>507.5865941010001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09435114956185189</v>
+        <v>0.09477479499143163</v>
       </c>
       <c r="T14">
-        <v>1.121273661936534</v>
+        <v>1.13105762104923</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.60475770230434</v>
+        <v>15.32746864828093</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08726023664254552</v>
+        <v>0.08705500167066137</v>
       </c>
       <c r="C15">
-        <v>2170.532588880617</v>
+        <v>2148.667049926529</v>
       </c>
       <c r="D15">
-        <v>2370.010588880617</v>
+        <v>2374.951049926529</v>
       </c>
       <c r="E15">
-        <v>-1252.522</v>
+        <v>-1225.716</v>
       </c>
       <c r="F15">
-        <v>348.478</v>
+        <v>375.284</v>
       </c>
       <c r="G15">
         <v>149</v>
@@ -2511,28 +2511,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M15">
-        <v>17.5284434</v>
+        <v>18.8767852</v>
       </c>
       <c r="N15">
-        <v>251.1382232666667</v>
+        <v>249.7898814666667</v>
       </c>
       <c r="O15">
-        <v>66.55162916566668</v>
+        <v>66.19431858866669</v>
       </c>
       <c r="P15">
-        <v>184.5865941010001</v>
+        <v>183.5955628780001</v>
       </c>
       <c r="Q15">
-        <v>507.5865941010001</v>
+        <v>506.5955628780001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09477479499143163</v>
+        <v>0.09520829264030392</v>
       </c>
       <c r="T15">
-        <v>1.13105762104923</v>
+        <v>1.141069114094779</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.32746864828093</v>
+        <v>14.232649459118</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08705500167066137</v>
+        <v>0.0868497666987772</v>
       </c>
       <c r="C16">
-        <v>2148.667049926529</v>
+        <v>2126.822151506571</v>
       </c>
       <c r="D16">
-        <v>2374.951049926529</v>
+        <v>2379.912151506571</v>
       </c>
       <c r="E16">
-        <v>-1225.716</v>
+        <v>-1198.91</v>
       </c>
       <c r="F16">
-        <v>375.284</v>
+        <v>402.09</v>
       </c>
       <c r="G16">
         <v>149</v>
@@ -2593,28 +2593,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M16">
-        <v>18.8767852</v>
+        <v>20.225127</v>
       </c>
       <c r="N16">
-        <v>249.7898814666667</v>
+        <v>248.4415396666668</v>
       </c>
       <c r="O16">
-        <v>66.19431858866669</v>
+        <v>65.8370080116667</v>
       </c>
       <c r="P16">
-        <v>183.5955628780001</v>
+        <v>182.6045316550001</v>
       </c>
       <c r="Q16">
-        <v>506.5955628780001</v>
+        <v>505.6045316550001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09520829264030392</v>
+        <v>0.09565199023385554</v>
       </c>
       <c r="T16">
-        <v>1.141069114094779</v>
+        <v>1.151316171682576</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.232649459118</v>
+        <v>13.28380616184347</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0868497666987772</v>
+        <v>0.08682093172689306</v>
       </c>
       <c r="C17">
-        <v>2126.822151506571</v>
+        <v>2100.714834268658</v>
       </c>
       <c r="D17">
-        <v>2379.912151506571</v>
+        <v>2380.610834268658</v>
       </c>
       <c r="E17">
-        <v>-1198.91</v>
+        <v>-1172.104</v>
       </c>
       <c r="F17">
-        <v>402.09</v>
+        <v>428.896</v>
       </c>
       <c r="G17">
         <v>149</v>
@@ -2675,45 +2675,45 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M17">
-        <v>20.225127</v>
+        <v>22.2168128</v>
       </c>
       <c r="N17">
-        <v>248.4415396666668</v>
+        <v>246.4498538666667</v>
       </c>
       <c r="O17">
-        <v>65.8370080116667</v>
+        <v>65.30921127466668</v>
       </c>
       <c r="P17">
-        <v>182.6045316550001</v>
+        <v>181.1406425920001</v>
       </c>
       <c r="Q17">
-        <v>505.6045316550001</v>
+        <v>504.1406425920001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09565199023385554</v>
+        <v>0.09610625205582508</v>
       </c>
       <c r="T17">
-        <v>1.151316171682576</v>
+        <v>1.161807206831988</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.265</v>
       </c>
       <c r="W17">
-        <v>0.0369705</v>
+        <v>0.038073</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.28380616184347</v>
+        <v>12.09294371273033</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08682093172689306</v>
+        <v>0.08662672175500889</v>
       </c>
       <c r="C18">
-        <v>2100.714834268658</v>
+        <v>2078.625326012345</v>
       </c>
       <c r="D18">
-        <v>2380.610834268658</v>
+        <v>2385.327326012345</v>
       </c>
       <c r="E18">
-        <v>-1172.104</v>
+        <v>-1145.298</v>
       </c>
       <c r="F18">
-        <v>428.896</v>
+        <v>455.702</v>
       </c>
       <c r="G18">
         <v>149</v>
@@ -2757,28 +2757,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M18">
-        <v>22.2168128</v>
+        <v>23.6053636</v>
       </c>
       <c r="N18">
-        <v>246.4498538666667</v>
+        <v>245.0613030666667</v>
       </c>
       <c r="O18">
-        <v>65.30921127466668</v>
+        <v>64.94124531266669</v>
       </c>
       <c r="P18">
-        <v>181.1406425920001</v>
+        <v>180.120057754</v>
       </c>
       <c r="Q18">
-        <v>504.1406425920001</v>
+        <v>503.1200577540001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09610625205582508</v>
+        <v>0.09657145994579386</v>
       </c>
       <c r="T18">
-        <v>1.161807206831988</v>
+        <v>1.172551038009096</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.09294371273033</v>
+        <v>11.38159408256972</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08662672175500889</v>
+        <v>0.08643251178312474</v>
       </c>
       <c r="C19">
-        <v>2078.625326012345</v>
+        <v>2056.554543584002</v>
       </c>
       <c r="D19">
-        <v>2385.327326012345</v>
+        <v>2390.062543584002</v>
       </c>
       <c r="E19">
-        <v>-1145.298</v>
+        <v>-1118.492</v>
       </c>
       <c r="F19">
-        <v>455.702</v>
+        <v>482.508</v>
       </c>
       <c r="G19">
         <v>149</v>
@@ -2839,28 +2839,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M19">
-        <v>23.6053636</v>
+        <v>24.9939144</v>
       </c>
       <c r="N19">
-        <v>245.0613030666667</v>
+        <v>243.6727522666667</v>
       </c>
       <c r="O19">
-        <v>64.94124531266669</v>
+        <v>64.5732793506667</v>
       </c>
       <c r="P19">
-        <v>180.120057754</v>
+        <v>179.0994729160001</v>
       </c>
       <c r="Q19">
-        <v>503.1200577540001</v>
+        <v>502.0994729160001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09657145994579386</v>
+        <v>0.09704801436966433</v>
       </c>
       <c r="T19">
-        <v>1.172551038009096</v>
+        <v>1.183556913849061</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.38159408256972</v>
+        <v>10.74928330020474</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08643251178312475</v>
+        <v>0.08623830181124061</v>
       </c>
       <c r="C20">
-        <v>2056.554543584002</v>
+        <v>2034.502598725835</v>
       </c>
       <c r="D20">
-        <v>2390.062543584002</v>
+        <v>2394.816598725834</v>
       </c>
       <c r="E20">
-        <v>-1118.492</v>
+        <v>-1091.686</v>
       </c>
       <c r="F20">
-        <v>482.508</v>
+        <v>509.314</v>
       </c>
       <c r="G20">
         <v>149</v>
@@ -2921,28 +2921,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M20">
-        <v>24.9939144</v>
+        <v>26.3824652</v>
       </c>
       <c r="N20">
-        <v>243.6727522666667</v>
+        <v>242.2842014666667</v>
       </c>
       <c r="O20">
-        <v>64.5732793506667</v>
+        <v>64.20531338866668</v>
       </c>
       <c r="P20">
-        <v>179.0994729160001</v>
+        <v>178.078888078</v>
       </c>
       <c r="Q20">
-        <v>502.0994729160001</v>
+        <v>501.078888078</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09704801436966433</v>
+        <v>0.09753633556943284</v>
       </c>
       <c r="T20">
-        <v>1.183556913849061</v>
+        <v>1.194834539709765</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.74928330020474</v>
+        <v>10.18353154756238</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08623830181124061</v>
+        <v>0.08629399183935643</v>
       </c>
       <c r="C21">
-        <v>2034.502598725835</v>
+        <v>2006.33143267371</v>
       </c>
       <c r="D21">
-        <v>2394.816598725834</v>
+        <v>2393.45143267371</v>
       </c>
       <c r="E21">
-        <v>-1091.686</v>
+        <v>-1064.88</v>
       </c>
       <c r="F21">
-        <v>509.314</v>
+        <v>536.12</v>
       </c>
       <c r="G21">
         <v>149</v>
@@ -3003,45 +3003,45 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M21">
-        <v>26.3824652</v>
+        <v>28.68242</v>
       </c>
       <c r="N21">
-        <v>242.2842014666667</v>
+        <v>239.9842466666667</v>
       </c>
       <c r="O21">
-        <v>64.20531338866668</v>
+        <v>63.59582536666669</v>
       </c>
       <c r="P21">
-        <v>178.078888078</v>
+        <v>176.3884213000001</v>
       </c>
       <c r="Q21">
-        <v>501.078888078</v>
+        <v>499.3884213000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09753633556943284</v>
+        <v>0.09803686479919554</v>
       </c>
       <c r="T21">
-        <v>1.194834539709765</v>
+        <v>1.206394106216988</v>
       </c>
       <c r="U21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0.265</v>
       </c>
       <c r="W21">
-        <v>0.038073</v>
+        <v>0.0393225</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>10.18353154756238</v>
+        <v>9.366945559916728</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08629399183935643</v>
+        <v>0.0861122768674723</v>
       </c>
       <c r="C22">
-        <v>2006.33143267371</v>
+        <v>1983.985687573445</v>
       </c>
       <c r="D22">
-        <v>2393.45143267371</v>
+        <v>2397.911687573445</v>
       </c>
       <c r="E22">
-        <v>-1064.88</v>
+        <v>-1038.074</v>
       </c>
       <c r="F22">
-        <v>536.12</v>
+        <v>562.926</v>
       </c>
       <c r="G22">
         <v>149</v>
@@ -3085,28 +3085,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M22">
-        <v>28.68242</v>
+        <v>30.116541</v>
       </c>
       <c r="N22">
-        <v>239.9842466666667</v>
+        <v>238.5501256666667</v>
       </c>
       <c r="O22">
-        <v>63.59582536666669</v>
+        <v>63.21578330166669</v>
       </c>
       <c r="P22">
-        <v>176.3884213000001</v>
+        <v>175.3343423650001</v>
       </c>
       <c r="Q22">
-        <v>499.3884213000001</v>
+        <v>498.3343423650001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09803686479919554</v>
+        <v>0.09855006565502822</v>
       </c>
       <c r="T22">
-        <v>1.206394106216988</v>
+        <v>1.218246319977557</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.366945559916728</v>
+        <v>8.920900533254025</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08611227686747229</v>
+        <v>0.08593056189558813</v>
       </c>
       <c r="C23">
-        <v>1983.985687573445</v>
+        <v>1961.656597096232</v>
       </c>
       <c r="D23">
-        <v>2397.911687573445</v>
+        <v>2402.388597096232</v>
       </c>
       <c r="E23">
-        <v>-1038.074</v>
+        <v>-1011.268</v>
       </c>
       <c r="F23">
-        <v>562.9259999999999</v>
+        <v>589.732</v>
       </c>
       <c r="G23">
         <v>149</v>
@@ -3167,28 +3167,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M23">
-        <v>30.11654099999999</v>
+        <v>31.550662</v>
       </c>
       <c r="N23">
-        <v>238.5501256666668</v>
+        <v>237.1160046666668</v>
       </c>
       <c r="O23">
-        <v>63.2157833016667</v>
+        <v>62.83574123666669</v>
       </c>
       <c r="P23">
-        <v>175.3343423650001</v>
+        <v>174.28026343</v>
       </c>
       <c r="Q23">
-        <v>498.3343423650001</v>
+        <v>497.28026343</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09855006565502822</v>
+        <v>0.09907642550716426</v>
       </c>
       <c r="T23">
-        <v>1.218246319977557</v>
+        <v>1.230402436655064</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.920900533254027</v>
+        <v>8.515405054469753</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08593056189558813</v>
+        <v>0.08574884692370398</v>
       </c>
       <c r="C24">
-        <v>1961.656597096232</v>
+        <v>1939.344254699276</v>
       </c>
       <c r="D24">
-        <v>2402.388597096232</v>
+        <v>2406.882254699276</v>
       </c>
       <c r="E24">
-        <v>-1011.268</v>
+        <v>-984.462</v>
       </c>
       <c r="F24">
-        <v>589.732</v>
+        <v>616.538</v>
       </c>
       <c r="G24">
         <v>149</v>
@@ -3249,28 +3249,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M24">
-        <v>31.550662</v>
+        <v>32.984783</v>
       </c>
       <c r="N24">
-        <v>237.1160046666668</v>
+        <v>235.6818836666667</v>
       </c>
       <c r="O24">
-        <v>62.83574123666669</v>
+        <v>62.45569917166669</v>
       </c>
       <c r="P24">
-        <v>174.28026343</v>
+        <v>173.226184495</v>
       </c>
       <c r="Q24">
-        <v>497.28026343</v>
+        <v>496.226184495</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09907642550716426</v>
+        <v>0.09961645704377139</v>
       </c>
       <c r="T24">
-        <v>1.230402436655064</v>
+        <v>1.242874296622896</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.515405054469753</v>
+        <v>8.145170052101502</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08574884692370398</v>
+        <v>0.08556713195181982</v>
       </c>
       <c r="C25">
-        <v>1939.344254699276</v>
+        <v>1917.048754540335</v>
       </c>
       <c r="D25">
-        <v>2406.882254699276</v>
+        <v>2411.392754540335</v>
       </c>
       <c r="E25">
-        <v>-984.462</v>
+        <v>-957.6559999999999</v>
       </c>
       <c r="F25">
-        <v>616.538</v>
+        <v>643.3440000000001</v>
       </c>
       <c r="G25">
         <v>149</v>
@@ -3331,28 +3331,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M25">
-        <v>32.984783</v>
+        <v>34.418904</v>
       </c>
       <c r="N25">
-        <v>235.6818836666667</v>
+        <v>234.2477626666667</v>
       </c>
       <c r="O25">
-        <v>62.45569917166669</v>
+        <v>62.07565710666669</v>
       </c>
       <c r="P25">
-        <v>173.226184495</v>
+        <v>172.1721055600001</v>
       </c>
       <c r="Q25">
-        <v>496.226184495</v>
+        <v>495.1721055600001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09961645704377139</v>
+        <v>0.100170699936605</v>
       </c>
       <c r="T25">
-        <v>1.242874296622896</v>
+        <v>1.255674363431987</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.145170052101502</v>
+        <v>7.805787966597272</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08556713195181982</v>
+        <v>0.08553241697993567</v>
       </c>
       <c r="C26">
-        <v>1917.048754540335</v>
+        <v>1891.106367985496</v>
       </c>
       <c r="D26">
-        <v>2411.392754540335</v>
+        <v>2412.256367985497</v>
       </c>
       <c r="E26">
-        <v>-957.6560000000001</v>
+        <v>-930.85</v>
       </c>
       <c r="F26">
-        <v>643.3439999999999</v>
+        <v>670.15</v>
       </c>
       <c r="G26">
         <v>149</v>
@@ -3413,45 +3413,45 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M26">
-        <v>34.418904</v>
+        <v>36.389145</v>
       </c>
       <c r="N26">
-        <v>234.2477626666667</v>
+        <v>232.2775216666668</v>
       </c>
       <c r="O26">
-        <v>62.07565710666669</v>
+        <v>61.55354324166669</v>
       </c>
       <c r="P26">
-        <v>172.1721055600001</v>
+        <v>170.7239784250001</v>
       </c>
       <c r="Q26">
-        <v>495.1721055600001</v>
+        <v>493.723978425</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.100170699936605</v>
+        <v>0.1007397226399142</v>
       </c>
       <c r="T26">
-        <v>1.255674363431987</v>
+        <v>1.268815765355987</v>
       </c>
       <c r="U26">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0.265</v>
       </c>
       <c r="W26">
-        <v>0.0393225</v>
+        <v>0.0399105</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.805787966597274</v>
+        <v>7.383154142991454</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08553241697993567</v>
+        <v>0.08535658200805152</v>
       </c>
       <c r="C27">
-        <v>1891.106367985496</v>
+        <v>1868.684179506692</v>
       </c>
       <c r="D27">
-        <v>2412.256367985497</v>
+        <v>2416.640179506692</v>
       </c>
       <c r="E27">
-        <v>-930.85</v>
+        <v>-904.044</v>
       </c>
       <c r="F27">
-        <v>670.15</v>
+        <v>696.956</v>
       </c>
       <c r="G27">
         <v>149</v>
@@ -3495,28 +3495,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M27">
-        <v>36.389145</v>
+        <v>37.8447108</v>
       </c>
       <c r="N27">
-        <v>232.2775216666668</v>
+        <v>230.8219558666667</v>
       </c>
       <c r="O27">
-        <v>61.55354324166669</v>
+        <v>61.16781830466669</v>
       </c>
       <c r="P27">
-        <v>170.7239784250001</v>
+        <v>169.654137562</v>
       </c>
       <c r="Q27">
-        <v>493.723978425</v>
+        <v>492.6541375620001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1007397226399142</v>
+        <v>0.1013241243352048</v>
       </c>
       <c r="T27">
-        <v>1.268815765355987</v>
+        <v>1.28231234030496</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.383154142991454</v>
+        <v>7.09918667595332</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08535658200805152</v>
+        <v>0.08518074703616735</v>
       </c>
       <c r="C28">
-        <v>1868.684179506692</v>
+        <v>1846.277953503477</v>
       </c>
       <c r="D28">
-        <v>2416.640179506692</v>
+        <v>2421.039953503478</v>
       </c>
       <c r="E28">
-        <v>-904.044</v>
+        <v>-877.2379999999999</v>
       </c>
       <c r="F28">
-        <v>696.956</v>
+        <v>723.7620000000001</v>
       </c>
       <c r="G28">
         <v>149</v>
@@ -3577,28 +3577,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M28">
-        <v>37.8447108</v>
+        <v>39.3002766</v>
       </c>
       <c r="N28">
-        <v>230.8219558666667</v>
+        <v>229.3663900666667</v>
       </c>
       <c r="O28">
-        <v>61.16781830466669</v>
+        <v>60.78209336766668</v>
       </c>
       <c r="P28">
-        <v>169.654137562</v>
+        <v>168.584296699</v>
       </c>
       <c r="Q28">
-        <v>492.6541375620001</v>
+        <v>491.584296699</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1013241243352048</v>
+        <v>0.1019245370358457</v>
       </c>
       <c r="T28">
-        <v>1.28231234030496</v>
+        <v>1.296178684430617</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.09918667595332</v>
+        <v>6.836253836103197</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08518074703616735</v>
+        <v>0.08500491206428321</v>
       </c>
       <c r="C29">
-        <v>1846.277953503477</v>
+        <v>1823.887777319491</v>
       </c>
       <c r="D29">
-        <v>2421.039953503478</v>
+        <v>2425.455777319492</v>
       </c>
       <c r="E29">
-        <v>-877.2379999999999</v>
+        <v>-850.4319999999999</v>
       </c>
       <c r="F29">
-        <v>723.7620000000001</v>
+        <v>750.5680000000001</v>
       </c>
       <c r="G29">
         <v>149</v>
@@ -3659,28 +3659,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M29">
-        <v>39.3002766</v>
+        <v>40.75584240000001</v>
       </c>
       <c r="N29">
-        <v>229.3663900666667</v>
+        <v>227.9108242666667</v>
       </c>
       <c r="O29">
-        <v>60.78209336766668</v>
+        <v>60.39636843066669</v>
       </c>
       <c r="P29">
-        <v>168.584296699</v>
+        <v>167.5144558360001</v>
       </c>
       <c r="Q29">
-        <v>491.584296699</v>
+        <v>490.514455836</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1019245370358457</v>
+        <v>0.10254162786706</v>
       </c>
       <c r="T29">
-        <v>1.296178684430617</v>
+        <v>1.310430204781986</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.836253836103197</v>
+        <v>6.592101913385226</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08500491206428321</v>
+        <v>0.08482907709239906</v>
       </c>
       <c r="C30">
-        <v>1823.887777319491</v>
+        <v>1801.513738936775</v>
       </c>
       <c r="D30">
-        <v>2425.455777319492</v>
+        <v>2429.887738936775</v>
       </c>
       <c r="E30">
-        <v>-850.4319999999999</v>
+        <v>-823.626</v>
       </c>
       <c r="F30">
-        <v>750.5680000000001</v>
+        <v>777.374</v>
       </c>
       <c r="G30">
         <v>149</v>
@@ -3741,28 +3741,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M30">
-        <v>40.75584240000001</v>
+        <v>42.2114082</v>
       </c>
       <c r="N30">
-        <v>227.9108242666667</v>
+        <v>226.4552584666667</v>
       </c>
       <c r="O30">
-        <v>60.39636843066669</v>
+        <v>60.01064349366669</v>
       </c>
       <c r="P30">
-        <v>167.5144558360001</v>
+        <v>166.4446149730001</v>
       </c>
       <c r="Q30">
-        <v>490.514455836</v>
+        <v>489.4446149730001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.10254162786706</v>
+        <v>0.1031761015385902</v>
       </c>
       <c r="T30">
-        <v>1.310430204781986</v>
+        <v>1.32508317641086</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.592101913385226</v>
+        <v>6.364788054302977</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08482907709239906</v>
+        <v>0.08465324212051489</v>
       </c>
       <c r="C31">
-        <v>1801.513738936776</v>
+        <v>1779.155926981615</v>
       </c>
       <c r="D31">
-        <v>2429.887738936775</v>
+        <v>2434.335926981615</v>
       </c>
       <c r="E31">
-        <v>-823.6260000000001</v>
+        <v>-796.8200000000001</v>
       </c>
       <c r="F31">
-        <v>777.3739999999999</v>
+        <v>804.1799999999999</v>
       </c>
       <c r="G31">
         <v>149</v>
@@ -3823,28 +3823,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M31">
-        <v>42.21140819999999</v>
+        <v>43.666974</v>
       </c>
       <c r="N31">
-        <v>226.4552584666667</v>
+        <v>224.9996926666668</v>
       </c>
       <c r="O31">
-        <v>60.01064349366669</v>
+        <v>59.62491855666669</v>
       </c>
       <c r="P31">
-        <v>166.4446149730001</v>
+        <v>165.3747741100001</v>
       </c>
       <c r="Q31">
-        <v>489.4446149730001</v>
+        <v>488.3747741100001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1031761015385902</v>
+        <v>0.103828703029307</v>
       </c>
       <c r="T31">
-        <v>1.32508317641086</v>
+        <v>1.340154804371986</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.364788054302978</v>
+        <v>6.152628452492879</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08465324212051489</v>
+        <v>0.08470525714863074</v>
       </c>
       <c r="C32">
-        <v>1779.155926981615</v>
+        <v>1751.032380638117</v>
       </c>
       <c r="D32">
-        <v>2434.335926981615</v>
+        <v>2433.018380638117</v>
       </c>
       <c r="E32">
-        <v>-796.8200000000001</v>
+        <v>-770.014</v>
       </c>
       <c r="F32">
-        <v>804.1799999999999</v>
+        <v>830.986</v>
       </c>
       <c r="G32">
         <v>149</v>
@@ -3905,45 +3905,45 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M32">
-        <v>43.666974</v>
+        <v>45.9535258</v>
       </c>
       <c r="N32">
-        <v>224.9996926666668</v>
+        <v>222.7131408666667</v>
       </c>
       <c r="O32">
-        <v>59.62491855666669</v>
+        <v>59.01898232966669</v>
       </c>
       <c r="P32">
-        <v>165.3747741100001</v>
+        <v>163.694158537</v>
       </c>
       <c r="Q32">
-        <v>488.3747741100001</v>
+        <v>486.694158537</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.103828703029307</v>
+        <v>0.1045002205052619</v>
       </c>
       <c r="T32">
-        <v>1.340154804371986</v>
+        <v>1.355663291114595</v>
       </c>
       <c r="U32">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V32">
         <v>0.265</v>
       </c>
       <c r="W32">
-        <v>0.0399105</v>
+        <v>0.0406455</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>6.152628452492879</v>
+        <v>5.846486466260806</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08470525714863074</v>
+        <v>0.08453677217674657</v>
       </c>
       <c r="C33">
-        <v>1751.032380638117</v>
+        <v>1728.499304582763</v>
       </c>
       <c r="D33">
-        <v>2433.018380638117</v>
+        <v>2437.291304582763</v>
       </c>
       <c r="E33">
-        <v>-770.014</v>
+        <v>-743.208</v>
       </c>
       <c r="F33">
-        <v>830.986</v>
+        <v>857.792</v>
       </c>
       <c r="G33">
         <v>149</v>
@@ -3987,28 +3987,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M33">
-        <v>45.9535258</v>
+        <v>47.4358976</v>
       </c>
       <c r="N33">
-        <v>222.7131408666667</v>
+        <v>221.2307690666667</v>
       </c>
       <c r="O33">
-        <v>59.01898232966669</v>
+        <v>58.62615380266669</v>
       </c>
       <c r="P33">
-        <v>163.694158537</v>
+        <v>162.604615264</v>
       </c>
       <c r="Q33">
-        <v>486.694158537</v>
+        <v>485.604615264</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1045002205052619</v>
+        <v>0.1051914884952156</v>
       </c>
       <c r="T33">
-        <v>1.355663291114595</v>
+        <v>1.371627909820221</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.846486466260806</v>
+        <v>5.663783764190154</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08453677217674657</v>
+        <v>0.08436828720486242</v>
       </c>
       <c r="C34">
-        <v>1728.499304582763</v>
+        <v>1705.981263350416</v>
       </c>
       <c r="D34">
-        <v>2437.291304582763</v>
+        <v>2441.579263350416</v>
       </c>
       <c r="E34">
-        <v>-743.208</v>
+        <v>-716.402</v>
       </c>
       <c r="F34">
-        <v>857.792</v>
+        <v>884.598</v>
       </c>
       <c r="G34">
         <v>149</v>
@@ -4069,28 +4069,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M34">
-        <v>47.4358976</v>
+        <v>48.9182694</v>
       </c>
       <c r="N34">
-        <v>221.2307690666667</v>
+        <v>219.7483972666668</v>
       </c>
       <c r="O34">
-        <v>58.62615380266669</v>
+        <v>58.23332527566669</v>
       </c>
       <c r="P34">
-        <v>162.604615264</v>
+        <v>161.5150719910001</v>
       </c>
       <c r="Q34">
-        <v>485.604615264</v>
+        <v>484.5150719910001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1051914884952156</v>
+        <v>0.1059033913505409</v>
       </c>
       <c r="T34">
-        <v>1.371627909820221</v>
+        <v>1.388069084308105</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.663783764190154</v>
+        <v>5.49215395315409</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08436828720486242</v>
+        <v>0.08419980223297827</v>
       </c>
       <c r="C35">
-        <v>1705.981263350416</v>
+        <v>1683.478336433818</v>
       </c>
       <c r="D35">
-        <v>2441.579263350416</v>
+        <v>2445.882336433818</v>
       </c>
       <c r="E35">
-        <v>-716.402</v>
+        <v>-689.596</v>
       </c>
       <c r="F35">
-        <v>884.598</v>
+        <v>911.404</v>
       </c>
       <c r="G35">
         <v>149</v>
@@ -4151,28 +4151,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M35">
-        <v>48.9182694</v>
+        <v>50.4006412</v>
       </c>
       <c r="N35">
-        <v>219.7483972666668</v>
+        <v>218.2660254666667</v>
       </c>
       <c r="O35">
-        <v>58.23332527566669</v>
+        <v>57.84049674866669</v>
       </c>
       <c r="P35">
-        <v>161.5150719910001</v>
+        <v>160.4255287180001</v>
       </c>
       <c r="Q35">
-        <v>484.5150719910001</v>
+        <v>483.4255287180001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1059033913505409</v>
+        <v>0.106636867019664</v>
       </c>
       <c r="T35">
-        <v>1.388069084308105</v>
+        <v>1.405008476204713</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.49215395315409</v>
+        <v>5.33062001335544</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08419980223297827</v>
+        <v>0.08403131726109411</v>
       </c>
       <c r="C36">
-        <v>1683.478336433818</v>
+        <v>1660.990603887095</v>
       </c>
       <c r="D36">
-        <v>2445.882336433818</v>
+        <v>2450.200603887095</v>
       </c>
       <c r="E36">
-        <v>-689.596</v>
+        <v>-662.79</v>
       </c>
       <c r="F36">
-        <v>911.404</v>
+        <v>938.21</v>
       </c>
       <c r="G36">
         <v>149</v>
@@ -4233,28 +4233,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M36">
-        <v>50.4006412</v>
+        <v>51.88301300000001</v>
       </c>
       <c r="N36">
-        <v>218.2660254666667</v>
+        <v>216.7836536666667</v>
       </c>
       <c r="O36">
-        <v>57.84049674866669</v>
+        <v>57.44766822166669</v>
       </c>
       <c r="P36">
-        <v>160.4255287180001</v>
+        <v>159.3359854450001</v>
       </c>
       <c r="Q36">
-        <v>483.4255287180001</v>
+        <v>482.3359854450001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.106636867019664</v>
+        <v>0.107392911170914</v>
       </c>
       <c r="T36">
-        <v>1.405008476204713</v>
+        <v>1.422469080159678</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.33062001335544</v>
+        <v>5.178316584402427</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08403131726109411</v>
+        <v>0.08386283228920997</v>
       </c>
       <c r="C37">
-        <v>1660.990603887095</v>
+        <v>1638.518146330724</v>
       </c>
       <c r="D37">
-        <v>2450.200603887095</v>
+        <v>2454.534146330724</v>
       </c>
       <c r="E37">
-        <v>-662.79</v>
+        <v>-635.9839999999999</v>
       </c>
       <c r="F37">
-        <v>938.21</v>
+        <v>965.0160000000001</v>
       </c>
       <c r="G37">
         <v>149</v>
@@ -4315,28 +4315,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M37">
-        <v>51.88301300000001</v>
+        <v>53.36538480000001</v>
       </c>
       <c r="N37">
-        <v>216.7836536666667</v>
+        <v>215.3012818666667</v>
       </c>
       <c r="O37">
-        <v>57.44766822166669</v>
+        <v>57.05483969466668</v>
       </c>
       <c r="P37">
-        <v>159.3359854450001</v>
+        <v>158.2464421720001</v>
       </c>
       <c r="Q37">
-        <v>482.3359854450001</v>
+        <v>481.2464421720001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.107392911170914</v>
+        <v>0.1081725817018906</v>
       </c>
       <c r="T37">
-        <v>1.422469080159678</v>
+        <v>1.440475327988235</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.178316584402427</v>
+        <v>5.034474457057915</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08386283228920997</v>
+        <v>0.08369434731732581</v>
       </c>
       <c r="C38">
-        <v>1638.518146330724</v>
+        <v>1616.061044956548</v>
       </c>
       <c r="D38">
-        <v>2454.534146330724</v>
+        <v>2458.883044956548</v>
       </c>
       <c r="E38">
-        <v>-635.984</v>
+        <v>-609.178</v>
       </c>
       <c r="F38">
-        <v>965.016</v>
+        <v>991.822</v>
       </c>
       <c r="G38">
         <v>149</v>
@@ -4397,28 +4397,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M38">
-        <v>53.3653848</v>
+        <v>54.8477566</v>
       </c>
       <c r="N38">
-        <v>215.3012818666667</v>
+        <v>213.8189100666667</v>
       </c>
       <c r="O38">
-        <v>57.05483969466668</v>
+        <v>56.66201116766669</v>
       </c>
       <c r="P38">
-        <v>158.2464421720001</v>
+        <v>157.1568988990001</v>
       </c>
       <c r="Q38">
-        <v>481.2464421720001</v>
+        <v>480.1568988990001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1081725817018906</v>
+        <v>0.1089770036782949</v>
       </c>
       <c r="T38">
-        <v>1.440475327988235</v>
+        <v>1.459053202731985</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.034474457057915</v>
+        <v>4.898407579840134</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08369434731732581</v>
+        <v>0.08352586234544165</v>
       </c>
       <c r="C39">
-        <v>1616.061044956548</v>
+        <v>1593.61938153285</v>
       </c>
       <c r="D39">
-        <v>2458.883044956548</v>
+        <v>2463.247381532849</v>
       </c>
       <c r="E39">
-        <v>-609.178</v>
+        <v>-582.3720000000001</v>
       </c>
       <c r="F39">
-        <v>991.822</v>
+        <v>1018.628</v>
       </c>
       <c r="G39">
         <v>149</v>
@@ -4479,28 +4479,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M39">
-        <v>54.8477566</v>
+        <v>56.3301284</v>
       </c>
       <c r="N39">
-        <v>213.8189100666667</v>
+        <v>212.3365382666667</v>
       </c>
       <c r="O39">
-        <v>56.66201116766669</v>
+        <v>56.26918264066668</v>
       </c>
       <c r="P39">
-        <v>157.1568988990001</v>
+        <v>156.0673556260001</v>
       </c>
       <c r="Q39">
-        <v>480.1568988990001</v>
+        <v>479.0673556260001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1089770036782949</v>
+        <v>0.1098073747507123</v>
       </c>
       <c r="T39">
-        <v>1.459053202731985</v>
+        <v>1.478230363757791</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.898407579840134</v>
+        <v>4.769502117212761</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08352586234544165</v>
+        <v>0.0833573773735575</v>
       </c>
       <c r="C40">
-        <v>1593.61938153285</v>
+        <v>1571.193238409475</v>
       </c>
       <c r="D40">
-        <v>2463.247381532849</v>
+        <v>2467.627238409475</v>
       </c>
       <c r="E40">
-        <v>-582.3720000000001</v>
+        <v>-555.566</v>
       </c>
       <c r="F40">
-        <v>1018.628</v>
+        <v>1045.434</v>
       </c>
       <c r="G40">
         <v>149</v>
@@ -4561,28 +4561,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M40">
-        <v>56.3301284</v>
+        <v>57.8125002</v>
       </c>
       <c r="N40">
-        <v>212.3365382666667</v>
+        <v>210.8541664666668</v>
       </c>
       <c r="O40">
-        <v>56.26918264066668</v>
+        <v>55.87635411366669</v>
       </c>
       <c r="P40">
-        <v>156.0673556260001</v>
+        <v>154.977812353</v>
       </c>
       <c r="Q40">
-        <v>479.0673556260001</v>
+        <v>477.977812353</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1098073747507123</v>
+        <v>0.1106649711041926</v>
       </c>
       <c r="T40">
-        <v>1.478230363757791</v>
+        <v>1.498036284161493</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.769502117212761</v>
+        <v>4.647207191130384</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0833573773735575</v>
+        <v>0.08318889240167335</v>
       </c>
       <c r="C41">
-        <v>1571.193238409475</v>
+        <v>1548.78269852301</v>
       </c>
       <c r="D41">
-        <v>2467.627238409475</v>
+        <v>2472.02269852301</v>
       </c>
       <c r="E41">
-        <v>-555.566</v>
+        <v>-528.76</v>
       </c>
       <c r="F41">
-        <v>1045.434</v>
+        <v>1072.24</v>
       </c>
       <c r="G41">
         <v>149</v>
@@ -4643,28 +4643,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M41">
-        <v>57.8125002</v>
+        <v>59.29487200000001</v>
       </c>
       <c r="N41">
-        <v>210.8541664666668</v>
+        <v>209.3717946666667</v>
       </c>
       <c r="O41">
-        <v>55.87635411366669</v>
+        <v>55.48352558666669</v>
       </c>
       <c r="P41">
-        <v>154.977812353</v>
+        <v>153.88826908</v>
       </c>
       <c r="Q41">
-        <v>477.977812353</v>
+        <v>476.88826908</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1106649711041926</v>
+        <v>0.1115511540027889</v>
       </c>
       <c r="T41">
-        <v>1.498036284161493</v>
+        <v>1.518502401911984</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.647207191130384</v>
+        <v>4.531027011352124</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08318889240167335</v>
+        <v>0.0837737824297892</v>
       </c>
       <c r="C42">
-        <v>1548.78269852301</v>
+        <v>1506.784764106784</v>
       </c>
       <c r="D42">
-        <v>2472.02269852301</v>
+        <v>2456.830764106784</v>
       </c>
       <c r="E42">
-        <v>-528.76</v>
+        <v>-501.954</v>
       </c>
       <c r="F42">
-        <v>1072.24</v>
+        <v>1099.046</v>
       </c>
       <c r="G42">
         <v>149</v>
@@ -4725,45 +4725,45 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M42">
-        <v>59.29487200000001</v>
+        <v>63.5248588</v>
       </c>
       <c r="N42">
-        <v>209.3717946666667</v>
+        <v>205.1418078666667</v>
       </c>
       <c r="O42">
-        <v>55.48352558666669</v>
+        <v>54.36257908466669</v>
       </c>
       <c r="P42">
-        <v>153.88826908</v>
+        <v>150.779228782</v>
       </c>
       <c r="Q42">
-        <v>476.88826908</v>
+        <v>473.779228782</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1115511540027889</v>
+        <v>0.1124673769996427</v>
       </c>
       <c r="T42">
-        <v>1.518502401911984</v>
+        <v>1.539662286365882</v>
       </c>
       <c r="U42">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V42">
         <v>0.265</v>
       </c>
       <c r="W42">
-        <v>0.0406455</v>
+        <v>0.042483</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.531027011352124</v>
+        <v>4.229315448185879</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0837737824297892</v>
+        <v>0.08362367245790503</v>
       </c>
       <c r="C43">
-        <v>1506.784764106784</v>
+        <v>1483.859880929848</v>
       </c>
       <c r="D43">
-        <v>2456.830764106784</v>
+        <v>2460.711880929849</v>
       </c>
       <c r="E43">
-        <v>-501.954</v>
+        <v>-475.1479999999999</v>
       </c>
       <c r="F43">
-        <v>1099.046</v>
+        <v>1125.852</v>
       </c>
       <c r="G43">
         <v>149</v>
@@ -4807,28 +4807,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M43">
-        <v>63.5248588</v>
+        <v>65.07424560000001</v>
       </c>
       <c r="N43">
-        <v>205.1418078666667</v>
+        <v>203.5924210666667</v>
       </c>
       <c r="O43">
-        <v>54.36257908466669</v>
+        <v>53.95199158266669</v>
       </c>
       <c r="P43">
-        <v>150.779228782</v>
+        <v>149.640429484</v>
       </c>
       <c r="Q43">
-        <v>473.779228782</v>
+        <v>472.640429484</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1124673769996427</v>
+        <v>0.1134151938929397</v>
       </c>
       <c r="T43">
-        <v>1.539662286365882</v>
+        <v>1.561551822007846</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.229315448185879</v>
+        <v>4.128617461324311</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08362367245790504</v>
+        <v>0.08347356248602089</v>
       </c>
       <c r="C44">
-        <v>1483.859880929848</v>
+        <v>1460.94727934851</v>
       </c>
       <c r="D44">
-        <v>2460.711880929848</v>
+        <v>2464.60527934851</v>
       </c>
       <c r="E44">
-        <v>-475.1480000000001</v>
+        <v>-448.3420000000001</v>
       </c>
       <c r="F44">
-        <v>1125.852</v>
+        <v>1152.658</v>
       </c>
       <c r="G44">
         <v>149</v>
@@ -4889,28 +4889,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M44">
-        <v>65.0742456</v>
+        <v>66.62363240000001</v>
       </c>
       <c r="N44">
-        <v>203.5924210666668</v>
+        <v>202.0430342666667</v>
       </c>
       <c r="O44">
-        <v>53.95199158266669</v>
+        <v>53.54140408066669</v>
       </c>
       <c r="P44">
-        <v>149.6404294840001</v>
+        <v>148.501630186</v>
       </c>
       <c r="Q44">
-        <v>472.640429484</v>
+        <v>471.5016301860001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1134151938929397</v>
+        <v>0.1143962675193349</v>
       </c>
       <c r="T44">
-        <v>1.561551822007846</v>
+        <v>1.584209411531984</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.128617461324312</v>
+        <v>4.032603101758629</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08347356248602089</v>
+        <v>0.08445535251413673</v>
       </c>
       <c r="C45">
-        <v>1460.94727934851</v>
+        <v>1408.89756070388</v>
       </c>
       <c r="D45">
-        <v>2464.60527934851</v>
+        <v>2439.36156070388</v>
       </c>
       <c r="E45">
-        <v>-448.3420000000001</v>
+        <v>-421.5360000000001</v>
       </c>
       <c r="F45">
-        <v>1152.658</v>
+        <v>1179.464</v>
       </c>
       <c r="G45">
         <v>149</v>
@@ -4971,45 +4971,45 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M45">
-        <v>66.62363240000001</v>
+        <v>72.3011432</v>
       </c>
       <c r="N45">
-        <v>202.0430342666667</v>
+        <v>196.3655234666667</v>
       </c>
       <c r="O45">
-        <v>53.54140408066669</v>
+        <v>52.03686371866669</v>
       </c>
       <c r="P45">
-        <v>148.501630186</v>
+        <v>144.328659748</v>
       </c>
       <c r="Q45">
-        <v>471.5016301860001</v>
+        <v>467.3286597480001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1143962675193349</v>
+        <v>0.1154123794895299</v>
       </c>
       <c r="T45">
-        <v>1.584209411531984</v>
+        <v>1.607676200681984</v>
       </c>
       <c r="U45">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V45">
         <v>0.265</v>
       </c>
       <c r="W45">
-        <v>0.042483</v>
+        <v>0.0450555</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>4.032603101758629</v>
+        <v>3.715939399789003</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08445535251413673</v>
+        <v>0.08433096754225258</v>
       </c>
       <c r="C46">
-        <v>1408.89756070388</v>
+        <v>1385.261094255216</v>
       </c>
       <c r="D46">
-        <v>2439.36156070388</v>
+        <v>2442.531094255216</v>
       </c>
       <c r="E46">
-        <v>-421.5360000000001</v>
+        <v>-394.73</v>
       </c>
       <c r="F46">
-        <v>1179.464</v>
+        <v>1206.27</v>
       </c>
       <c r="G46">
         <v>149</v>
@@ -5053,28 +5053,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M46">
-        <v>72.3011432</v>
+        <v>73.944351</v>
       </c>
       <c r="N46">
-        <v>196.3655234666667</v>
+        <v>194.7223156666668</v>
       </c>
       <c r="O46">
-        <v>52.03686371866669</v>
+        <v>51.6014136516667</v>
       </c>
       <c r="P46">
-        <v>144.328659748</v>
+        <v>143.1209020150001</v>
       </c>
       <c r="Q46">
-        <v>467.3286597480001</v>
+        <v>466.1209020150001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1154123794895299</v>
+        <v>0.1164654409859138</v>
       </c>
       <c r="T46">
-        <v>1.607676200681984</v>
+        <v>1.631996327619256</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.715939399789003</v>
+        <v>3.633362968682581</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08433096754225258</v>
+        <v>0.08420658257036842</v>
       </c>
       <c r="C47">
-        <v>1385.261094255216</v>
+        <v>1361.632875057033</v>
       </c>
       <c r="D47">
-        <v>2442.531094255216</v>
+        <v>2445.708875057033</v>
       </c>
       <c r="E47">
-        <v>-394.73</v>
+        <v>-367.924</v>
       </c>
       <c r="F47">
-        <v>1206.27</v>
+        <v>1233.076</v>
       </c>
       <c r="G47">
         <v>149</v>
@@ -5135,28 +5135,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M47">
-        <v>73.944351</v>
+        <v>75.5875588</v>
       </c>
       <c r="N47">
-        <v>194.7223156666668</v>
+        <v>193.0791078666667</v>
       </c>
       <c r="O47">
-        <v>51.6014136516667</v>
+        <v>51.16596358466668</v>
       </c>
       <c r="P47">
-        <v>143.1209020150001</v>
+        <v>141.913144282</v>
       </c>
       <c r="Q47">
-        <v>466.1209020150001</v>
+        <v>464.9131442820001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1164654409859138</v>
+        <v>0.1175575047599415</v>
       </c>
       <c r="T47">
-        <v>1.631996327619256</v>
+        <v>1.65721719999865</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.633362968682581</v>
+        <v>3.554376817189481</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08420658257036842</v>
+        <v>0.08504945759848426</v>
       </c>
       <c r="C48">
-        <v>1361.632875057033</v>
+        <v>1313.453562204647</v>
       </c>
       <c r="D48">
-        <v>2445.708875057033</v>
+        <v>2424.335562204647</v>
       </c>
       <c r="E48">
-        <v>-367.924</v>
+        <v>-341.1179999999999</v>
       </c>
       <c r="F48">
-        <v>1233.076</v>
+        <v>1259.882</v>
       </c>
       <c r="G48">
         <v>149</v>
@@ -5217,45 +5217,45 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M48">
-        <v>75.5875588</v>
+        <v>80.75843620000001</v>
       </c>
       <c r="N48">
-        <v>193.0791078666667</v>
+        <v>187.9082304666667</v>
       </c>
       <c r="O48">
-        <v>51.16596358466668</v>
+        <v>49.79568107366669</v>
       </c>
       <c r="P48">
-        <v>141.913144282</v>
+        <v>138.1125493930001</v>
       </c>
       <c r="Q48">
-        <v>464.9131442820001</v>
+        <v>461.1125493930001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1175575047599415</v>
+        <v>0.1186907784877062</v>
       </c>
       <c r="T48">
-        <v>1.65721719999865</v>
+        <v>1.683389803411228</v>
       </c>
       <c r="U48">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V48">
         <v>0.265</v>
       </c>
       <c r="W48">
-        <v>0.0450555</v>
+        <v>0.0471135</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>3.554376817189481</v>
+        <v>3.326793822521624</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08504945759848426</v>
+        <v>0.08494565262660012</v>
       </c>
       <c r="C49">
-        <v>1313.453562204647</v>
+        <v>1289.25961802739</v>
       </c>
       <c r="D49">
-        <v>2424.335562204647</v>
+        <v>2426.94761802739</v>
       </c>
       <c r="E49">
-        <v>-341.1179999999999</v>
+        <v>-314.3119999999999</v>
       </c>
       <c r="F49">
-        <v>1259.882</v>
+        <v>1286.688</v>
       </c>
       <c r="G49">
         <v>149</v>
@@ -5299,28 +5299,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M49">
-        <v>80.75843620000001</v>
+        <v>82.47670080000002</v>
       </c>
       <c r="N49">
-        <v>187.9082304666667</v>
+        <v>186.1899658666667</v>
       </c>
       <c r="O49">
-        <v>49.79568107366669</v>
+        <v>49.34034095466669</v>
       </c>
       <c r="P49">
-        <v>138.1125493930001</v>
+        <v>136.8496249120001</v>
       </c>
       <c r="Q49">
-        <v>461.1125493930001</v>
+        <v>459.8496249120001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1186907784877062</v>
+        <v>0.1198676396665387</v>
       </c>
       <c r="T49">
-        <v>1.683389803411228</v>
+        <v>1.710569045416598</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.326793822521624</v>
+        <v>3.257485617885757</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08494565262660012</v>
+        <v>0.08484184765471595</v>
       </c>
       <c r="C50">
-        <v>1289.259618027391</v>
+        <v>1265.071308544271</v>
       </c>
       <c r="D50">
-        <v>2426.94761802739</v>
+        <v>2429.565308544271</v>
       </c>
       <c r="E50">
-        <v>-314.3120000000001</v>
+        <v>-287.5060000000001</v>
       </c>
       <c r="F50">
-        <v>1286.688</v>
+        <v>1313.494</v>
       </c>
       <c r="G50">
         <v>149</v>
@@ -5381,28 +5381,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M50">
-        <v>82.4767008</v>
+        <v>84.1949654</v>
       </c>
       <c r="N50">
-        <v>186.1899658666667</v>
+        <v>184.4717012666667</v>
       </c>
       <c r="O50">
-        <v>49.34034095466669</v>
+        <v>48.88500083566669</v>
       </c>
       <c r="P50">
-        <v>136.8496249120001</v>
+        <v>135.5867004310001</v>
       </c>
       <c r="Q50">
-        <v>459.8496249120001</v>
+        <v>458.5867004310001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1198676396665387</v>
+        <v>0.1210906522641489</v>
       </c>
       <c r="T50">
-        <v>1.710569045416598</v>
+        <v>1.738814140049629</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.257485617885757</v>
+        <v>3.191006319561558</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08484184765471595</v>
+        <v>0.0847380426828318</v>
       </c>
       <c r="C51">
-        <v>1265.071308544271</v>
+        <v>1240.888652007612</v>
       </c>
       <c r="D51">
-        <v>2429.565308544271</v>
+        <v>2432.188652007612</v>
       </c>
       <c r="E51">
-        <v>-287.5060000000001</v>
+        <v>-260.7</v>
       </c>
       <c r="F51">
-        <v>1313.494</v>
+        <v>1340.3</v>
       </c>
       <c r="G51">
         <v>149</v>
@@ -5463,28 +5463,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M51">
-        <v>84.1949654</v>
+        <v>85.91323</v>
       </c>
       <c r="N51">
-        <v>184.4717012666667</v>
+        <v>182.7534366666667</v>
       </c>
       <c r="O51">
-        <v>48.88500083566669</v>
+        <v>48.42966071666669</v>
       </c>
       <c r="P51">
-        <v>135.5867004310001</v>
+        <v>134.3237759500001</v>
       </c>
       <c r="Q51">
-        <v>458.5867004310001</v>
+        <v>457.32377595</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1210906522641489</v>
+        <v>0.1223625853656636</v>
       </c>
       <c r="T51">
-        <v>1.738814140049629</v>
+        <v>1.768189038467982</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.191006319561558</v>
+        <v>3.127186193170327</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.0847380426828318</v>
+        <v>0.08463423771094765</v>
       </c>
       <c r="C52">
-        <v>1240.888652007612</v>
+        <v>1216.711666748656</v>
       </c>
       <c r="D52">
-        <v>2432.188652007612</v>
+        <v>2434.817666748656</v>
       </c>
       <c r="E52">
-        <v>-260.7</v>
+        <v>-233.894</v>
       </c>
       <c r="F52">
-        <v>1340.3</v>
+        <v>1367.106</v>
       </c>
       <c r="G52">
         <v>149</v>
@@ -5545,28 +5545,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M52">
-        <v>85.91323</v>
+        <v>87.63149460000001</v>
       </c>
       <c r="N52">
-        <v>182.7534366666667</v>
+        <v>181.0351720666667</v>
       </c>
       <c r="O52">
-        <v>48.42966071666669</v>
+        <v>47.97432059766669</v>
       </c>
       <c r="P52">
-        <v>134.3237759500001</v>
+        <v>133.0608514690001</v>
       </c>
       <c r="Q52">
-        <v>457.32377595</v>
+        <v>456.0608514690001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1223625853656636</v>
+        <v>0.1236864341039748</v>
       </c>
       <c r="T52">
-        <v>1.768189038467982</v>
+        <v>1.798762912331982</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.127186193170327</v>
+        <v>3.065868816833654</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08463423771094765</v>
+        <v>0.08453043273906349</v>
       </c>
       <c r="C53">
-        <v>1216.711666748656</v>
+        <v>1192.540371177991</v>
       </c>
       <c r="D53">
-        <v>2434.817666748656</v>
+        <v>2437.452371177991</v>
       </c>
       <c r="E53">
-        <v>-233.894</v>
+        <v>-207.088</v>
       </c>
       <c r="F53">
-        <v>1367.106</v>
+        <v>1393.912</v>
       </c>
       <c r="G53">
         <v>149</v>
@@ -5627,28 +5627,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M53">
-        <v>87.63149460000001</v>
+        <v>89.34975920000001</v>
       </c>
       <c r="N53">
-        <v>181.0351720666667</v>
+        <v>179.3169074666667</v>
       </c>
       <c r="O53">
-        <v>47.97432059766669</v>
+        <v>47.51898047866669</v>
       </c>
       <c r="P53">
-        <v>133.0608514690001</v>
+        <v>131.7979269880001</v>
       </c>
       <c r="Q53">
-        <v>456.0608514690001</v>
+        <v>454.7979269880001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1236864341039748</v>
+        <v>0.1250654432063823</v>
       </c>
       <c r="T53">
-        <v>1.798762912331982</v>
+        <v>1.830610697606981</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.065868816833654</v>
+        <v>3.006909801125314</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08453043273906349</v>
+        <v>0.08746511776717934</v>
       </c>
       <c r="C54">
-        <v>1192.540371177991</v>
+        <v>1093.381104769267</v>
       </c>
       <c r="D54">
-        <v>2437.452371177991</v>
+        <v>2365.099104769267</v>
       </c>
       <c r="E54">
-        <v>-207.088</v>
+        <v>-180.2819999999999</v>
       </c>
       <c r="F54">
-        <v>1393.912</v>
+        <v>1420.718</v>
       </c>
       <c r="G54">
         <v>149</v>
@@ -5709,45 +5709,45 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M54">
-        <v>89.34975920000001</v>
+        <v>102.1496242</v>
       </c>
       <c r="N54">
-        <v>179.3169074666667</v>
+        <v>166.5170424666667</v>
       </c>
       <c r="O54">
-        <v>47.51898047866669</v>
+        <v>44.12701625366669</v>
       </c>
       <c r="P54">
-        <v>131.7979269880001</v>
+        <v>122.3900262130001</v>
       </c>
       <c r="Q54">
-        <v>454.7979269880001</v>
+        <v>445.3900262130001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1250654432063823</v>
+        <v>0.1265031335471901</v>
       </c>
       <c r="T54">
-        <v>1.830610697606981</v>
+        <v>1.8638137077873</v>
       </c>
       <c r="U54">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V54">
         <v>0.265</v>
       </c>
       <c r="W54">
-        <v>0.0471135</v>
+        <v>0.0528465</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>3.006909801125314</v>
+        <v>2.630128781880205</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08746511776717934</v>
+        <v>0.08741864279529518</v>
       </c>
       <c r="C55">
-        <v>1093.381104769267</v>
+        <v>1067.687433594795</v>
       </c>
       <c r="D55">
-        <v>2365.099104769267</v>
+        <v>2366.211433594795</v>
       </c>
       <c r="E55">
-        <v>-180.2819999999999</v>
+        <v>-153.4759999999999</v>
       </c>
       <c r="F55">
-        <v>1420.718</v>
+        <v>1447.524</v>
       </c>
       <c r="G55">
         <v>149</v>
@@ -5791,28 +5791,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M55">
-        <v>102.1496242</v>
+        <v>104.0769756</v>
       </c>
       <c r="N55">
-        <v>166.5170424666667</v>
+        <v>164.5896910666667</v>
       </c>
       <c r="O55">
-        <v>44.12701625366669</v>
+        <v>43.61626813266668</v>
       </c>
       <c r="P55">
-        <v>122.3900262130001</v>
+        <v>120.973422934</v>
       </c>
       <c r="Q55">
-        <v>445.3900262130001</v>
+        <v>443.973422934</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1265031335471901</v>
+        <v>0.1280033321636852</v>
       </c>
       <c r="T55">
-        <v>1.8638137077873</v>
+        <v>1.898460327105894</v>
       </c>
       <c r="U55">
         <v>0.07190000000000001</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.630128781880205</v>
+        <v>2.581422693326868</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08741864279529518</v>
+        <v>0.08737216782341103</v>
       </c>
       <c r="C56">
-        <v>1067.687433594795</v>
+        <v>1041.994809190491</v>
       </c>
       <c r="D56">
-        <v>2366.211433594795</v>
+        <v>2367.324809190491</v>
       </c>
       <c r="E56">
-        <v>-153.4759999999999</v>
+        <v>-126.6699999999998</v>
       </c>
       <c r="F56">
-        <v>1447.524</v>
+        <v>1474.33</v>
       </c>
       <c r="G56">
         <v>149</v>
@@ -5873,28 +5873,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M56">
-        <v>104.0769756</v>
+        <v>106.004327</v>
       </c>
       <c r="N56">
-        <v>164.5896910666667</v>
+        <v>162.6623396666667</v>
       </c>
       <c r="O56">
-        <v>43.61626813266668</v>
+        <v>43.10552001166668</v>
       </c>
       <c r="P56">
-        <v>120.973422934</v>
+        <v>119.556819655</v>
       </c>
       <c r="Q56">
-        <v>443.973422934</v>
+        <v>442.556819655</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1280033321636852</v>
+        <v>0.1295702062742467</v>
       </c>
       <c r="T56">
-        <v>1.898460327105894</v>
+        <v>1.93464679617198</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.581422693326868</v>
+        <v>2.534487735266379</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08737216782341103</v>
+        <v>0.08893093285152687</v>
       </c>
       <c r="C57">
-        <v>1041.994809190491</v>
+        <v>978.4091927412831</v>
       </c>
       <c r="D57">
-        <v>2367.324809190491</v>
+        <v>2330.545192741283</v>
       </c>
       <c r="E57">
-        <v>-126.6699999999998</v>
+        <v>-99.86399999999981</v>
       </c>
       <c r="F57">
-        <v>1474.33</v>
+        <v>1501.136</v>
       </c>
       <c r="G57">
         <v>149</v>
@@ -5955,45 +5955,45 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M57">
-        <v>106.004327</v>
+        <v>113.7861088</v>
       </c>
       <c r="N57">
-        <v>162.6623396666667</v>
+        <v>154.8805578666667</v>
       </c>
       <c r="O57">
-        <v>43.10552001166668</v>
+        <v>41.04334783466668</v>
       </c>
       <c r="P57">
-        <v>119.556819655</v>
+        <v>113.837210032</v>
       </c>
       <c r="Q57">
-        <v>442.556819655</v>
+        <v>436.837210032</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1295702062742467</v>
+        <v>0.1312083019352883</v>
       </c>
       <c r="T57">
-        <v>1.93464679617198</v>
+        <v>1.972478104741071</v>
       </c>
       <c r="U57">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V57">
         <v>0.265</v>
       </c>
       <c r="W57">
-        <v>0.0528465</v>
+        <v>0.05571300000000001</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.534487735266379</v>
+        <v>2.361155236786397</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08893093285152687</v>
+        <v>0.08891312287964272</v>
       </c>
       <c r="C58">
-        <v>978.4091927412831</v>
+        <v>952.0169699406993</v>
       </c>
       <c r="D58">
-        <v>2330.545192741283</v>
+        <v>2330.958969940699</v>
       </c>
       <c r="E58">
-        <v>-99.86399999999981</v>
+        <v>-73.05799999999999</v>
       </c>
       <c r="F58">
-        <v>1501.136</v>
+        <v>1527.942</v>
       </c>
       <c r="G58">
         <v>149</v>
@@ -6037,28 +6037,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M58">
-        <v>113.7861088</v>
+        <v>115.8180036</v>
       </c>
       <c r="N58">
-        <v>154.8805578666667</v>
+        <v>152.8486630666667</v>
       </c>
       <c r="O58">
-        <v>41.04334783466668</v>
+        <v>40.50489571266669</v>
       </c>
       <c r="P58">
-        <v>113.837210032</v>
+        <v>112.3437673540001</v>
       </c>
       <c r="Q58">
-        <v>436.837210032</v>
+        <v>435.3437673540001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1312083019352883</v>
+        <v>0.1329225880921924</v>
       </c>
       <c r="T58">
-        <v>1.972478104741071</v>
+        <v>2.012069009057561</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.361155236786397</v>
+        <v>2.319731460702425</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08891312287964272</v>
+        <v>0.08889531290775857</v>
       </c>
       <c r="C59">
-        <v>952.0169699406993</v>
+        <v>925.6248940945488</v>
       </c>
       <c r="D59">
-        <v>2330.958969940699</v>
+        <v>2331.372894094549</v>
       </c>
       <c r="E59">
-        <v>-73.05799999999999</v>
+        <v>-46.25199999999995</v>
       </c>
       <c r="F59">
-        <v>1527.942</v>
+        <v>1554.748</v>
       </c>
       <c r="G59">
         <v>149</v>
@@ -6119,28 +6119,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M59">
-        <v>115.8180036</v>
+        <v>117.8498984</v>
       </c>
       <c r="N59">
-        <v>152.8486630666667</v>
+        <v>150.8167682666667</v>
       </c>
       <c r="O59">
-        <v>40.50489571266669</v>
+        <v>39.96644359066668</v>
       </c>
       <c r="P59">
-        <v>112.3437673540001</v>
+        <v>110.850324676</v>
       </c>
       <c r="Q59">
-        <v>435.3437673540001</v>
+        <v>433.850324676</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1329225880921924</v>
+        <v>0.1347185069232347</v>
       </c>
       <c r="T59">
-        <v>2.012069009057561</v>
+        <v>2.05354519453198</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.319731460702425</v>
+        <v>2.279736090690314</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08889531290775857</v>
+        <v>0.0888775029358744</v>
       </c>
       <c r="C60">
-        <v>925.6248940945491</v>
+        <v>899.2329652811329</v>
       </c>
       <c r="D60">
-        <v>2331.372894094549</v>
+        <v>2331.786965281133</v>
       </c>
       <c r="E60">
-        <v>-46.25200000000018</v>
+        <v>-19.44600000000014</v>
       </c>
       <c r="F60">
-        <v>1554.748</v>
+        <v>1581.554</v>
       </c>
       <c r="G60">
         <v>149</v>
@@ -6201,28 +6201,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M60">
-        <v>117.8498984</v>
+        <v>119.8817932</v>
       </c>
       <c r="N60">
-        <v>150.8167682666667</v>
+        <v>148.7848734666667</v>
       </c>
       <c r="O60">
-        <v>39.96644359066669</v>
+        <v>39.42799146866669</v>
       </c>
       <c r="P60">
-        <v>110.8503246760001</v>
+        <v>109.356881998</v>
       </c>
       <c r="Q60">
-        <v>433.8503246760001</v>
+        <v>432.3568819980001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1347185069232347</v>
+        <v>0.1366020315509132</v>
       </c>
       <c r="T60">
-        <v>2.053545194531979</v>
+        <v>2.097044608566125</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.279736090690315</v>
+        <v>2.241096495932851</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.0888775029358744</v>
+        <v>0.08885969296399025</v>
       </c>
       <c r="C61">
-        <v>899.2329652811329</v>
+        <v>872.8411835788072</v>
       </c>
       <c r="D61">
-        <v>2331.786965281133</v>
+        <v>2332.201183578807</v>
       </c>
       <c r="E61">
-        <v>-19.44600000000014</v>
+        <v>7.3599999999999</v>
       </c>
       <c r="F61">
-        <v>1581.554</v>
+        <v>1608.36</v>
       </c>
       <c r="G61">
         <v>149</v>
@@ -6283,28 +6283,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M61">
-        <v>119.8817932</v>
+        <v>121.913688</v>
       </c>
       <c r="N61">
-        <v>148.7848734666667</v>
+        <v>146.7529786666667</v>
       </c>
       <c r="O61">
-        <v>39.42799146866669</v>
+        <v>38.88953934666669</v>
       </c>
       <c r="P61">
-        <v>109.356881998</v>
+        <v>107.8634393200001</v>
       </c>
       <c r="Q61">
-        <v>432.3568819980001</v>
+        <v>430.8634393200001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1366020315509132</v>
+        <v>0.1385797324099756</v>
       </c>
       <c r="T61">
-        <v>2.097044608566125</v>
+        <v>2.142718993301978</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.241096495932851</v>
+        <v>2.203744887667304</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08885969296399025</v>
+        <v>0.0888418829921061</v>
       </c>
       <c r="C62">
-        <v>872.8411835788072</v>
+        <v>846.4495490659845</v>
       </c>
       <c r="D62">
-        <v>2332.201183578807</v>
+        <v>2332.615549065984</v>
       </c>
       <c r="E62">
-        <v>7.3599999999999</v>
+        <v>34.16599999999994</v>
       </c>
       <c r="F62">
-        <v>1608.36</v>
+        <v>1635.166</v>
       </c>
       <c r="G62">
         <v>149</v>
@@ -6365,28 +6365,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M62">
-        <v>121.913688</v>
+        <v>123.9455828</v>
       </c>
       <c r="N62">
-        <v>146.7529786666667</v>
+        <v>144.7210838666667</v>
       </c>
       <c r="O62">
-        <v>38.88953934666669</v>
+        <v>38.35108722466668</v>
       </c>
       <c r="P62">
-        <v>107.8634393200001</v>
+        <v>106.369996642</v>
       </c>
       <c r="Q62">
-        <v>430.8634393200001</v>
+        <v>429.369996642</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1385797324099756</v>
+        <v>0.1406588538259131</v>
       </c>
       <c r="T62">
-        <v>2.142718993301978</v>
+        <v>2.190735654178131</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.203744887667304</v>
+        <v>2.167617922295709</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.0888418829921061</v>
+        <v>0.08882407302022195</v>
       </c>
       <c r="C63">
-        <v>846.4495490659845</v>
+        <v>820.0580618211332</v>
       </c>
       <c r="D63">
-        <v>2332.615549065984</v>
+        <v>2333.030061821133</v>
       </c>
       <c r="E63">
-        <v>34.16599999999994</v>
+        <v>60.97199999999998</v>
       </c>
       <c r="F63">
-        <v>1635.166</v>
+        <v>1661.972</v>
       </c>
       <c r="G63">
         <v>149</v>
@@ -6447,28 +6447,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M63">
-        <v>123.9455828</v>
+        <v>125.9774776</v>
       </c>
       <c r="N63">
-        <v>144.7210838666667</v>
+        <v>142.6891890666667</v>
       </c>
       <c r="O63">
-        <v>38.35108722466668</v>
+        <v>37.81263510266668</v>
       </c>
       <c r="P63">
-        <v>106.369996642</v>
+        <v>104.876553964</v>
       </c>
       <c r="Q63">
-        <v>429.369996642</v>
+        <v>427.876553964</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1406588538259131</v>
+        <v>0.1428474026847946</v>
       </c>
       <c r="T63">
-        <v>2.190735654178131</v>
+        <v>2.241279507731977</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.167617922295709</v>
+        <v>2.132656342903842</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08882407302022195</v>
+        <v>0.08880626304833779</v>
       </c>
       <c r="C64">
-        <v>820.0580618211332</v>
+        <v>793.6667219227772</v>
       </c>
       <c r="D64">
-        <v>2333.030061821133</v>
+        <v>2333.444721922777</v>
       </c>
       <c r="E64">
-        <v>60.97199999999998</v>
+        <v>87.77800000000002</v>
       </c>
       <c r="F64">
-        <v>1661.972</v>
+        <v>1688.778</v>
       </c>
       <c r="G64">
         <v>149</v>
@@ -6529,28 +6529,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M64">
-        <v>125.9774776</v>
+        <v>128.0093724</v>
       </c>
       <c r="N64">
-        <v>142.6891890666667</v>
+        <v>140.6572942666667</v>
       </c>
       <c r="O64">
-        <v>37.81263510266668</v>
+        <v>37.27418298066669</v>
       </c>
       <c r="P64">
-        <v>104.876553964</v>
+        <v>103.383111286</v>
       </c>
       <c r="Q64">
-        <v>427.876553964</v>
+        <v>426.383111286</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1428474026847946</v>
+        <v>0.145154251481994</v>
       </c>
       <c r="T64">
-        <v>2.241279507731977</v>
+        <v>2.294555461477922</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.132656342903842</v>
+        <v>2.098804654921242</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08880626304833779</v>
+        <v>0.08878845307645362</v>
       </c>
       <c r="C65">
-        <v>793.6667219227772</v>
+        <v>767.2755294494957</v>
       </c>
       <c r="D65">
-        <v>2333.444721922777</v>
+        <v>2333.859529449496</v>
       </c>
       <c r="E65">
-        <v>87.77800000000002</v>
+        <v>114.5840000000001</v>
       </c>
       <c r="F65">
-        <v>1688.778</v>
+        <v>1715.584</v>
       </c>
       <c r="G65">
         <v>149</v>
@@ -6611,28 +6611,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M65">
-        <v>128.0093724</v>
+        <v>130.0412672</v>
       </c>
       <c r="N65">
-        <v>140.6572942666667</v>
+        <v>138.6253994666667</v>
       </c>
       <c r="O65">
-        <v>37.27418298066669</v>
+        <v>36.73573085866668</v>
       </c>
       <c r="P65">
-        <v>103.383111286</v>
+        <v>101.889668608</v>
       </c>
       <c r="Q65">
-        <v>426.383111286</v>
+        <v>424.889668608</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.145154251481994</v>
+        <v>0.1475892585457045</v>
       </c>
       <c r="T65">
-        <v>2.294555461477922</v>
+        <v>2.350791190431976</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.098804654921242</v>
+        <v>2.066010832188097</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08878845307645362</v>
+        <v>0.08877064310456949</v>
       </c>
       <c r="C66">
-        <v>767.2755294494957</v>
+        <v>740.8844844799239</v>
       </c>
       <c r="D66">
-        <v>2333.859529449496</v>
+        <v>2334.274484479924</v>
       </c>
       <c r="E66">
-        <v>114.5840000000001</v>
+        <v>141.3900000000001</v>
       </c>
       <c r="F66">
-        <v>1715.584</v>
+        <v>1742.39</v>
       </c>
       <c r="G66">
         <v>149</v>
@@ -6693,28 +6693,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M66">
-        <v>130.0412672</v>
+        <v>132.073162</v>
       </c>
       <c r="N66">
-        <v>138.6253994666667</v>
+        <v>136.5935046666667</v>
       </c>
       <c r="O66">
-        <v>36.73573085866668</v>
+        <v>36.19727873666668</v>
       </c>
       <c r="P66">
-        <v>101.889668608</v>
+        <v>100.39622593</v>
       </c>
       <c r="Q66">
-        <v>424.889668608</v>
+        <v>423.39622593</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1475892585457045</v>
+        <v>0.1501634088701985</v>
       </c>
       <c r="T66">
-        <v>2.350791190431976</v>
+        <v>2.410240389611976</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.066010832188097</v>
+        <v>2.034226050154434</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08877064310456949</v>
+        <v>0.08875283313268532</v>
       </c>
       <c r="C67">
-        <v>740.8844844799239</v>
+        <v>714.4935870927548</v>
       </c>
       <c r="D67">
-        <v>2334.274484479924</v>
+        <v>2334.689587092755</v>
       </c>
       <c r="E67">
-        <v>141.3900000000001</v>
+        <v>168.1959999999999</v>
       </c>
       <c r="F67">
-        <v>1742.39</v>
+        <v>1769.196</v>
       </c>
       <c r="G67">
         <v>149</v>
@@ -6775,28 +6775,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M67">
-        <v>132.073162</v>
+        <v>134.1050568</v>
       </c>
       <c r="N67">
-        <v>136.5935046666667</v>
+        <v>134.5616098666667</v>
       </c>
       <c r="O67">
-        <v>36.19727873666668</v>
+        <v>35.65882661466669</v>
       </c>
       <c r="P67">
-        <v>100.39622593</v>
+        <v>98.90278325200006</v>
       </c>
       <c r="Q67">
-        <v>423.39622593</v>
+        <v>421.9027832520001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1501634088701985</v>
+        <v>0.1528889798020157</v>
       </c>
       <c r="T67">
-        <v>2.410240389611976</v>
+        <v>2.473186600508445</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.034226050154434</v>
+        <v>2.003404443333912</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08875283313268532</v>
+        <v>0.09572781316080117</v>
       </c>
       <c r="C68">
-        <v>714.4935870927548</v>
+        <v>535.6772250065401</v>
       </c>
       <c r="D68">
-        <v>2334.689587092755</v>
+        <v>2182.67922500654</v>
       </c>
       <c r="E68">
-        <v>168.1959999999999</v>
+        <v>195.002</v>
       </c>
       <c r="F68">
-        <v>1769.196</v>
+        <v>1796.002</v>
       </c>
       <c r="G68">
         <v>149</v>
@@ -6857,45 +6857,45 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M68">
-        <v>134.1050568</v>
+        <v>161.64018</v>
       </c>
       <c r="N68">
-        <v>134.5616098666667</v>
+        <v>107.0264866666668</v>
       </c>
       <c r="O68">
-        <v>35.65882661466669</v>
+        <v>28.36201896666669</v>
       </c>
       <c r="P68">
-        <v>98.90278325200006</v>
+        <v>78.66446770000006</v>
       </c>
       <c r="Q68">
-        <v>421.9027832520001</v>
+        <v>401.6644677</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1528889798020157</v>
+        <v>0.1557797368509126</v>
       </c>
       <c r="T68">
-        <v>2.473186600508445</v>
+        <v>2.539947733277429</v>
       </c>
       <c r="U68">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V68">
         <v>0.265</v>
       </c>
       <c r="W68">
-        <v>0.05571300000000001</v>
+        <v>0.06615</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y68">
-        <v>2.003404443333912</v>
+        <v>1.662127984927181</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09572781316080117</v>
+        <v>0.09581437318891702</v>
       </c>
       <c r="C69">
-        <v>535.6772250065401</v>
+        <v>507.1090152215966</v>
       </c>
       <c r="D69">
-        <v>2182.67922500654</v>
+        <v>2180.917015221597</v>
       </c>
       <c r="E69">
-        <v>195.002</v>
+        <v>221.808</v>
       </c>
       <c r="F69">
-        <v>1796.002</v>
+        <v>1822.808</v>
       </c>
       <c r="G69">
         <v>149</v>
@@ -6939,28 +6939,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M69">
-        <v>161.64018</v>
+        <v>164.05272</v>
       </c>
       <c r="N69">
-        <v>107.0264866666668</v>
+        <v>104.6139466666667</v>
       </c>
       <c r="O69">
-        <v>28.36201896666669</v>
+        <v>27.72269586666669</v>
       </c>
       <c r="P69">
-        <v>78.66446770000006</v>
+        <v>76.89125080000005</v>
       </c>
       <c r="Q69">
-        <v>401.6644677</v>
+        <v>399.8912508000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1557797368509126</v>
+        <v>0.1588511662153657</v>
       </c>
       <c r="T69">
-        <v>2.539947733277429</v>
+        <v>2.610881436844474</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.662127984927181</v>
+        <v>1.63768492632531</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09581437318891702</v>
+        <v>0.09590093321703286</v>
       </c>
       <c r="C70">
-        <v>507.1090152215966</v>
+        <v>478.5436486196077</v>
       </c>
       <c r="D70">
-        <v>2180.917015221597</v>
+        <v>2179.157648619608</v>
       </c>
       <c r="E70">
-        <v>221.808</v>
+        <v>248.614</v>
       </c>
       <c r="F70">
-        <v>1822.808</v>
+        <v>1849.614</v>
       </c>
       <c r="G70">
         <v>149</v>
@@ -7021,28 +7021,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M70">
-        <v>164.05272</v>
+        <v>166.46526</v>
       </c>
       <c r="N70">
-        <v>104.6139466666667</v>
+        <v>102.2014066666667</v>
       </c>
       <c r="O70">
-        <v>27.72269586666669</v>
+        <v>27.08337276666669</v>
       </c>
       <c r="P70">
-        <v>76.89125080000005</v>
+        <v>75.11803390000006</v>
       </c>
       <c r="Q70">
-        <v>399.8912508000001</v>
+        <v>398.1180339000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1588511662153657</v>
+        <v>0.1621207523130092</v>
       </c>
       <c r="T70">
-        <v>2.610881436844474</v>
+        <v>2.686391508383586</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.63768492632531</v>
+        <v>1.613950362175668</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09590093321703286</v>
+        <v>0.0959874932451487</v>
       </c>
       <c r="C71">
-        <v>478.5436486196077</v>
+        <v>449.9811183252509</v>
       </c>
       <c r="D71">
-        <v>2179.157648619608</v>
+        <v>2177.401118325251</v>
       </c>
       <c r="E71">
-        <v>248.614</v>
+        <v>275.4200000000001</v>
       </c>
       <c r="F71">
-        <v>1849.614</v>
+        <v>1876.42</v>
       </c>
       <c r="G71">
         <v>149</v>
@@ -7103,28 +7103,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M71">
-        <v>166.46526</v>
+        <v>168.8778</v>
       </c>
       <c r="N71">
-        <v>102.2014066666667</v>
+        <v>99.78886666666673</v>
       </c>
       <c r="O71">
-        <v>27.08337276666669</v>
+        <v>26.44404966666669</v>
       </c>
       <c r="P71">
-        <v>75.11803390000006</v>
+        <v>73.34481700000005</v>
       </c>
       <c r="Q71">
-        <v>398.1180339000001</v>
+        <v>396.344817</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1621207523130092</v>
+        <v>0.1656083108171623</v>
       </c>
       <c r="T71">
-        <v>2.686391508383586</v>
+        <v>2.766935584691972</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.613950362175668</v>
+        <v>1.590893928430301</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.0959874932451487</v>
+        <v>0.09607405327326456</v>
       </c>
       <c r="C72">
-        <v>449.9811183252509</v>
+        <v>421.4214174853537</v>
       </c>
       <c r="D72">
-        <v>2177.401118325251</v>
+        <v>2175.647417485354</v>
       </c>
       <c r="E72">
-        <v>275.4200000000001</v>
+        <v>302.2260000000001</v>
       </c>
       <c r="F72">
-        <v>1876.42</v>
+        <v>1903.226</v>
       </c>
       <c r="G72">
         <v>149</v>
@@ -7185,28 +7185,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M72">
-        <v>168.8778</v>
+        <v>171.29034</v>
       </c>
       <c r="N72">
-        <v>99.78886666666673</v>
+        <v>97.37632666666673</v>
       </c>
       <c r="O72">
-        <v>26.44404966666669</v>
+        <v>25.80472656666668</v>
       </c>
       <c r="P72">
-        <v>73.34481700000005</v>
+        <v>71.57160010000004</v>
       </c>
       <c r="Q72">
-        <v>396.344817</v>
+        <v>394.5716001000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1656083108171623</v>
+        <v>0.169336390597464</v>
       </c>
       <c r="T72">
-        <v>2.766935584691972</v>
+        <v>2.853034424883696</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.590893928430301</v>
+        <v>1.568486971691846</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09607405327326454</v>
+        <v>0.0961606133013804</v>
       </c>
       <c r="C73">
-        <v>421.4214174853539</v>
+        <v>392.8645392688047</v>
       </c>
       <c r="D73">
-        <v>2175.647417485354</v>
+        <v>2173.896539268805</v>
       </c>
       <c r="E73">
-        <v>302.2259999999999</v>
+        <v>329.0319999999999</v>
       </c>
       <c r="F73">
-        <v>1903.226</v>
+        <v>1930.032</v>
       </c>
       <c r="G73">
         <v>149</v>
@@ -7267,28 +7267,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M73">
-        <v>171.29034</v>
+        <v>173.70288</v>
       </c>
       <c r="N73">
-        <v>97.37632666666676</v>
+        <v>94.96378666666675</v>
       </c>
       <c r="O73">
-        <v>25.80472656666669</v>
+        <v>25.16540346666669</v>
       </c>
       <c r="P73">
-        <v>71.57160010000007</v>
+        <v>69.79838320000006</v>
       </c>
       <c r="Q73">
-        <v>394.5716001000001</v>
+        <v>392.7983832</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1693363905974639</v>
+        <v>0.1733307617906442</v>
       </c>
       <c r="T73">
-        <v>2.853034424883695</v>
+        <v>2.945283182231969</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.568486971691847</v>
+        <v>1.546702430418349</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.0961606133013804</v>
+        <v>0.09624717332949624</v>
       </c>
       <c r="C74">
-        <v>392.8645392688047</v>
+        <v>364.3104768664646</v>
       </c>
       <c r="D74">
-        <v>2173.896539268805</v>
+        <v>2172.148476866465</v>
       </c>
       <c r="E74">
-        <v>329.0319999999999</v>
+        <v>355.838</v>
       </c>
       <c r="F74">
-        <v>1930.032</v>
+        <v>1956.838</v>
       </c>
       <c r="G74">
         <v>149</v>
@@ -7349,28 +7349,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M74">
-        <v>173.70288</v>
+        <v>176.11542</v>
       </c>
       <c r="N74">
-        <v>94.96378666666675</v>
+        <v>92.55124666666674</v>
       </c>
       <c r="O74">
-        <v>25.16540346666669</v>
+        <v>24.52608036666669</v>
       </c>
       <c r="P74">
-        <v>69.79838320000006</v>
+        <v>68.02516630000005</v>
       </c>
       <c r="Q74">
-        <v>392.7983832</v>
+        <v>391.0251663</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1733307617906442</v>
+        <v>0.1776210123314675</v>
       </c>
       <c r="T74">
-        <v>2.945283182231969</v>
+        <v>3.044365180865302</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.546702430418349</v>
+        <v>1.52551472589207</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09624717332949624</v>
+        <v>0.09633373335761208</v>
       </c>
       <c r="C75">
-        <v>364.3104768664646</v>
+        <v>335.7592234910765</v>
       </c>
       <c r="D75">
-        <v>2172.148476866465</v>
+        <v>2170.403223491076</v>
       </c>
       <c r="E75">
-        <v>355.838</v>
+        <v>382.644</v>
       </c>
       <c r="F75">
-        <v>1956.838</v>
+        <v>1983.644</v>
       </c>
       <c r="G75">
         <v>149</v>
@@ -7431,28 +7431,28 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M75">
-        <v>176.11542</v>
+        <v>178.52796</v>
       </c>
       <c r="N75">
-        <v>92.55124666666674</v>
+        <v>90.13870666666674</v>
       </c>
       <c r="O75">
-        <v>24.52608036666669</v>
+        <v>23.88675726666668</v>
       </c>
       <c r="P75">
-        <v>68.02516630000005</v>
+        <v>66.25194940000006</v>
       </c>
       <c r="Q75">
-        <v>391.0251663</v>
+        <v>389.2519494000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1776210123314675</v>
+        <v>0.1822412821446619</v>
       </c>
       <c r="T75">
-        <v>3.044365180865302</v>
+        <v>3.151068871701198</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.52551472589207</v>
+        <v>1.504899662028663</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09633373335761208</v>
+        <v>0.131134350691308</v>
       </c>
       <c r="C76">
-        <v>335.7592234910765</v>
+        <v>-220.9667953244609</v>
       </c>
       <c r="D76">
-        <v>2170.403223491076</v>
+        <v>1640.483204675539</v>
       </c>
       <c r="E76">
-        <v>382.644</v>
+        <v>409.4499999999998</v>
       </c>
       <c r="F76">
-        <v>1983.644</v>
+        <v>2010.45</v>
       </c>
       <c r="G76">
         <v>149</v>
@@ -7513,45 +7513,45 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M76">
-        <v>178.52796</v>
+        <v>295.13406</v>
       </c>
       <c r="N76">
-        <v>90.13870666666674</v>
+        <v>-26.46739333333323</v>
       </c>
       <c r="O76">
-        <v>23.88675726666668</v>
+        <v>-7.013859233333307</v>
       </c>
       <c r="P76">
-        <v>66.25194940000006</v>
+        <v>-19.45353409999993</v>
       </c>
       <c r="Q76">
-        <v>389.2519494000001</v>
+        <v>303.5464659</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1822412821446619</v>
+        <v>0.1903772993058076</v>
       </c>
       <c r="T76">
-        <v>3.151068871701198</v>
+        <v>3.338967651404333</v>
       </c>
       <c r="U76">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.265</v>
+        <v>0.2412350057687909</v>
       </c>
       <c r="W76">
-        <v>0.06615</v>
+        <v>0.1113867011531415</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y76">
-        <v>1.504899662028663</v>
+        <v>0.9103207764860035</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.131134350691308</v>
+        <v>0.132144350691308</v>
       </c>
       <c r="C77">
-        <v>-220.9667953244609</v>
+        <v>-259.3155518100166</v>
       </c>
       <c r="D77">
-        <v>1640.483204675539</v>
+        <v>1628.940448189983</v>
       </c>
       <c r="E77">
-        <v>409.4499999999998</v>
+        <v>436.2559999999999</v>
       </c>
       <c r="F77">
-        <v>2010.45</v>
+        <v>2037.256</v>
       </c>
       <c r="G77">
         <v>149</v>
@@ -7595,37 +7595,37 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M77">
-        <v>295.13406</v>
+        <v>299.0691808</v>
       </c>
       <c r="N77">
-        <v>-26.46739333333323</v>
+        <v>-30.40251413333328</v>
       </c>
       <c r="O77">
-        <v>-7.013859233333307</v>
+        <v>-8.056666245333322</v>
       </c>
       <c r="P77">
-        <v>-19.45353409999993</v>
+        <v>-22.34584788799996</v>
       </c>
       <c r="Q77">
-        <v>303.5464659</v>
+        <v>300.654152112</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1903772993058076</v>
+        <v>0.1964013534435496</v>
       </c>
       <c r="T77">
-        <v>3.338967651404333</v>
+        <v>3.47809130354618</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.2412350057687909</v>
+        <v>0.2380608609560437</v>
       </c>
       <c r="W77">
-        <v>0.1113867011531415</v>
+        <v>0.1118526656116528</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.9103207764860035</v>
+        <v>0.8983428715322402</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.132144350691308</v>
+        <v>0.133154350691308</v>
       </c>
       <c r="C78">
-        <v>-259.3155518100166</v>
+        <v>-297.5030091024396</v>
       </c>
       <c r="D78">
-        <v>1628.940448189983</v>
+        <v>1617.55899089756</v>
       </c>
       <c r="E78">
-        <v>436.2559999999999</v>
+        <v>463.0619999999999</v>
       </c>
       <c r="F78">
-        <v>2037.256</v>
+        <v>2064.062</v>
       </c>
       <c r="G78">
         <v>149</v>
@@ -7677,37 +7677,37 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M78">
-        <v>299.0691808</v>
+        <v>303.0043016</v>
       </c>
       <c r="N78">
-        <v>-30.40251413333328</v>
+        <v>-34.33763493333328</v>
       </c>
       <c r="O78">
-        <v>-8.056666245333322</v>
+        <v>-9.099473257333319</v>
       </c>
       <c r="P78">
-        <v>-22.34584788799996</v>
+        <v>-25.23816167599996</v>
       </c>
       <c r="Q78">
-        <v>300.654152112</v>
+        <v>297.7618383240001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1964013534435496</v>
+        <v>0.2029492383758778</v>
       </c>
       <c r="T78">
-        <v>3.47809130354618</v>
+        <v>3.629312664569928</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.2380608609560437</v>
+        <v>0.234969161463108</v>
       </c>
       <c r="W78">
-        <v>0.1118526656116528</v>
+        <v>0.1123065270972158</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8983428715322402</v>
+        <v>0.8866760809928604</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.133154350691308</v>
+        <v>0.1341643506913081</v>
       </c>
       <c r="C79">
-        <v>-297.5030091024396</v>
+        <v>-335.532524749791</v>
       </c>
       <c r="D79">
-        <v>1617.55899089756</v>
+        <v>1606.335475250209</v>
       </c>
       <c r="E79">
-        <v>463.0619999999999</v>
+        <v>489.8679999999999</v>
       </c>
       <c r="F79">
-        <v>2064.062</v>
+        <v>2090.868</v>
       </c>
       <c r="G79">
         <v>149</v>
@@ -7759,37 +7759,37 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M79">
-        <v>303.0043016</v>
+        <v>306.9394224</v>
       </c>
       <c r="N79">
-        <v>-34.33763493333328</v>
+        <v>-38.27275573333327</v>
       </c>
       <c r="O79">
-        <v>-9.099473257333319</v>
+        <v>-10.14228026933332</v>
       </c>
       <c r="P79">
-        <v>-25.23816167599996</v>
+        <v>-28.13047546399995</v>
       </c>
       <c r="Q79">
-        <v>297.7618383240001</v>
+        <v>294.869524536</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2029492383758778</v>
+        <v>0.2100923855747814</v>
       </c>
       <c r="T79">
-        <v>3.629312664569928</v>
+        <v>3.794281422050379</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.234969161463108</v>
+        <v>0.2319567363161451</v>
       </c>
       <c r="W79">
-        <v>0.1123065270972158</v>
+        <v>0.1127487511087899</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8866760809928604</v>
+        <v>0.8753084389288495</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1341643506913081</v>
+        <v>0.135174350691308</v>
       </c>
       <c r="C80">
-        <v>-335.532524749791</v>
+        <v>-373.4073637561785</v>
       </c>
       <c r="D80">
-        <v>1606.335475250209</v>
+        <v>1595.266636243821</v>
       </c>
       <c r="E80">
-        <v>489.8679999999999</v>
+        <v>516.674</v>
       </c>
       <c r="F80">
-        <v>2090.868</v>
+        <v>2117.674</v>
       </c>
       <c r="G80">
         <v>149</v>
@@ -7841,37 +7841,37 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M80">
-        <v>306.9394224</v>
+        <v>310.8745432</v>
       </c>
       <c r="N80">
-        <v>-38.27275573333327</v>
+        <v>-42.20787653333326</v>
       </c>
       <c r="O80">
-        <v>-10.14228026933332</v>
+        <v>-11.18508728133332</v>
       </c>
       <c r="P80">
-        <v>-28.13047546399995</v>
+        <v>-31.02278925199995</v>
       </c>
       <c r="Q80">
-        <v>294.869524536</v>
+        <v>291.9772107480001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2100923855747814</v>
+        <v>0.2179158325069138</v>
       </c>
       <c r="T80">
-        <v>3.794281422050379</v>
+        <v>3.974961489767064</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.2319567363161451</v>
+        <v>0.2290205750969534</v>
       </c>
       <c r="W80">
-        <v>0.1127487511087899</v>
+        <v>0.1131797795757672</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8753084389288495</v>
+        <v>0.8642285852715222</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.135174350691308</v>
+        <v>0.136184350691308</v>
       </c>
       <c r="C81">
-        <v>-373.4073637561785</v>
+        <v>-411.1307017484173</v>
       </c>
       <c r="D81">
-        <v>1595.266636243821</v>
+        <v>1584.349298251583</v>
       </c>
       <c r="E81">
-        <v>516.674</v>
+        <v>543.48</v>
       </c>
       <c r="F81">
-        <v>2117.674</v>
+        <v>2144.48</v>
       </c>
       <c r="G81">
         <v>149</v>
@@ -7923,37 +7923,37 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M81">
-        <v>310.8745432</v>
+        <v>314.8096640000001</v>
       </c>
       <c r="N81">
-        <v>-42.20787653333326</v>
+        <v>-46.14299733333331</v>
       </c>
       <c r="O81">
-        <v>-11.18508728133332</v>
+        <v>-12.22789429333333</v>
       </c>
       <c r="P81">
-        <v>-31.02278925199995</v>
+        <v>-33.91510303999998</v>
       </c>
       <c r="Q81">
-        <v>291.9772107480001</v>
+        <v>289.08489696</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2179158325069138</v>
+        <v>0.2265216241322595</v>
       </c>
       <c r="T81">
-        <v>3.974961489767064</v>
+        <v>4.173709564255417</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.2290205750969534</v>
+        <v>0.2261578179082415</v>
       </c>
       <c r="W81">
-        <v>0.1131797795757672</v>
+        <v>0.1136000323310702</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8642285852715222</v>
+        <v>0.8534257279556281</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.136184350691308</v>
+        <v>0.137194350691308</v>
       </c>
       <c r="C82">
-        <v>-411.1307017484173</v>
+        <v>-448.7056280135457</v>
       </c>
       <c r="D82">
-        <v>1584.349298251583</v>
+        <v>1573.580371986454</v>
       </c>
       <c r="E82">
-        <v>543.48</v>
+        <v>570.2860000000001</v>
       </c>
       <c r="F82">
-        <v>2144.48</v>
+        <v>2171.286</v>
       </c>
       <c r="G82">
         <v>149</v>
@@ -8005,37 +8005,37 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M82">
-        <v>314.8096640000001</v>
+        <v>318.7447848</v>
       </c>
       <c r="N82">
-        <v>-46.14299733333331</v>
+        <v>-50.07811813333331</v>
       </c>
       <c r="O82">
-        <v>-12.22789429333333</v>
+        <v>-13.27070130533333</v>
       </c>
       <c r="P82">
-        <v>-33.91510303999998</v>
+        <v>-36.80741682799998</v>
       </c>
       <c r="Q82">
-        <v>289.08489696</v>
+        <v>286.192583172</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2265216241322595</v>
+        <v>0.2360332885602732</v>
       </c>
       <c r="T82">
-        <v>4.173709564255417</v>
+        <v>4.393378488689913</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.2261578179082415</v>
+        <v>0.2233657460822138</v>
       </c>
       <c r="W82">
-        <v>0.1136000323310702</v>
+        <v>0.114009908475131</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8534257279556281</v>
+        <v>0.8428896078574105</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.137194350691308</v>
+        <v>0.138204350691308</v>
       </c>
       <c r="C83">
-        <v>-448.7056280135457</v>
+        <v>-486.135148413302</v>
       </c>
       <c r="D83">
-        <v>1573.580371986454</v>
+        <v>1562.956851586698</v>
       </c>
       <c r="E83">
-        <v>570.2860000000001</v>
+        <v>597.0920000000001</v>
       </c>
       <c r="F83">
-        <v>2171.286</v>
+        <v>2198.092</v>
       </c>
       <c r="G83">
         <v>149</v>
@@ -8087,37 +8087,37 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M83">
-        <v>318.7447848</v>
+        <v>322.6799056</v>
       </c>
       <c r="N83">
-        <v>-50.07811813333331</v>
+        <v>-54.0132389333333</v>
       </c>
       <c r="O83">
-        <v>-13.27070130533333</v>
+        <v>-14.31350831733332</v>
       </c>
       <c r="P83">
-        <v>-36.80741682799998</v>
+        <v>-39.69973061599998</v>
       </c>
       <c r="Q83">
-        <v>286.192583172</v>
+        <v>283.300269384</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2360332885602732</v>
+        <v>0.2466018045913995</v>
       </c>
       <c r="T83">
-        <v>4.393378488689913</v>
+        <v>4.637455071394909</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.2233657460822138</v>
+        <v>0.2206417735690161</v>
       </c>
       <c r="W83">
-        <v>0.114009908475131</v>
+        <v>0.1144097876400685</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8428896078574105</v>
+        <v>0.8326104662981738</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.138204350691308</v>
+        <v>0.139214350691308</v>
       </c>
       <c r="C84">
-        <v>-486.135148413302</v>
+        <v>-523.4221881813326</v>
       </c>
       <c r="D84">
-        <v>1562.956851586698</v>
+        <v>1552.475811818668</v>
       </c>
       <c r="E84">
-        <v>597.0920000000001</v>
+        <v>623.8980000000001</v>
       </c>
       <c r="F84">
-        <v>2198.092</v>
+        <v>2224.898</v>
       </c>
       <c r="G84">
         <v>149</v>
@@ -8169,37 +8169,37 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M84">
-        <v>322.6799056</v>
+        <v>326.6150264</v>
       </c>
       <c r="N84">
-        <v>-54.0132389333333</v>
+        <v>-57.94835973333329</v>
       </c>
       <c r="O84">
-        <v>-14.31350831733332</v>
+        <v>-15.35631532933332</v>
       </c>
       <c r="P84">
-        <v>-39.69973061599998</v>
+        <v>-42.59204440399996</v>
       </c>
       <c r="Q84">
-        <v>283.300269384</v>
+        <v>280.407955596</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2466018045913995</v>
+        <v>0.2584136754497171</v>
       </c>
       <c r="T84">
-        <v>4.637455071394909</v>
+        <v>4.910246546182845</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.2206417735690161</v>
+        <v>0.2179834389477026</v>
       </c>
       <c r="W84">
-        <v>0.1144097876400685</v>
+        <v>0.1148000311624773</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8326104662981738</v>
+        <v>0.822579014896991</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.139214350691308</v>
+        <v>0.1402243506913081</v>
       </c>
       <c r="C85">
-        <v>-523.4221881813326</v>
+        <v>-560.5695946086105</v>
       </c>
       <c r="D85">
-        <v>1552.475811818668</v>
+        <v>1542.13440539139</v>
       </c>
       <c r="E85">
-        <v>623.8980000000001</v>
+        <v>650.7040000000002</v>
       </c>
       <c r="F85">
-        <v>2224.898</v>
+        <v>2251.704</v>
       </c>
       <c r="G85">
         <v>149</v>
@@ -8251,37 +8251,37 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M85">
-        <v>326.6150264</v>
+        <v>330.5501472000001</v>
       </c>
       <c r="N85">
-        <v>-57.94835973333329</v>
+        <v>-61.88348053333334</v>
       </c>
       <c r="O85">
-        <v>-15.35631532933332</v>
+        <v>-16.39912234133334</v>
       </c>
       <c r="P85">
-        <v>-42.59204440399996</v>
+        <v>-45.484358192</v>
       </c>
       <c r="Q85">
-        <v>280.407955596</v>
+        <v>277.515641808</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2584136754497171</v>
+        <v>0.2717020301653245</v>
       </c>
       <c r="T85">
-        <v>4.910246546182845</v>
+        <v>5.217136955319273</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2179834389477026</v>
+        <v>0.215388398007849</v>
       </c>
       <c r="W85">
-        <v>0.1148000311624773</v>
+        <v>0.1151809831724478</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.822579014896991</v>
+        <v>0.8127864075767887</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.140224350691308</v>
+        <v>0.141234350691308</v>
       </c>
       <c r="C86">
-        <v>-560.5695946086096</v>
+        <v>-597.5801396222225</v>
       </c>
       <c r="D86">
-        <v>1542.13440539139</v>
+        <v>1531.929860377777</v>
       </c>
       <c r="E86">
-        <v>650.7039999999997</v>
+        <v>677.5099999999998</v>
       </c>
       <c r="F86">
-        <v>2251.704</v>
+        <v>2278.51</v>
       </c>
       <c r="G86">
         <v>149</v>
@@ -8333,37 +8333,37 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M86">
-        <v>330.5501472</v>
+        <v>334.485268</v>
       </c>
       <c r="N86">
-        <v>-61.88348053333323</v>
+        <v>-65.81860133333328</v>
       </c>
       <c r="O86">
-        <v>-16.39912234133331</v>
+        <v>-17.44192935333332</v>
       </c>
       <c r="P86">
-        <v>-45.48435819199992</v>
+        <v>-48.37667197999995</v>
       </c>
       <c r="Q86">
-        <v>277.5156418080001</v>
+        <v>274.62332802</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2717020301653243</v>
+        <v>0.2867621655096793</v>
       </c>
       <c r="T86">
-        <v>5.21713695531927</v>
+        <v>5.564946085673887</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2153883980078491</v>
+        <v>0.2128544168548155</v>
       </c>
       <c r="W86">
-        <v>0.1151809831724478</v>
+        <v>0.1155529716057131</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8127864075767889</v>
+        <v>0.8032242145464736</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.141234350691308</v>
+        <v>0.1908314333025218</v>
       </c>
       <c r="C87">
-        <v>-597.5801396222225</v>
+        <v>-1000.092122260941</v>
       </c>
       <c r="D87">
-        <v>1531.929860377777</v>
+        <v>1156.223877739058</v>
       </c>
       <c r="E87">
-        <v>677.5099999999998</v>
+        <v>704.3159999999998</v>
       </c>
       <c r="F87">
-        <v>2278.51</v>
+        <v>2305.316</v>
       </c>
       <c r="G87">
         <v>149</v>
@@ -8415,45 +8415,45 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M87">
-        <v>334.485268</v>
+        <v>462.9074528</v>
       </c>
       <c r="N87">
-        <v>-65.81860133333328</v>
+        <v>-194.2407861333332</v>
       </c>
       <c r="O87">
-        <v>-17.44192935333332</v>
+        <v>-51.47380832533332</v>
       </c>
       <c r="P87">
-        <v>-48.37667197999995</v>
+        <v>-142.7669778079999</v>
       </c>
       <c r="Q87">
-        <v>274.62332802</v>
+        <v>180.2330221920001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2867621655096793</v>
+        <v>0.3193100531261835</v>
       </c>
       <c r="T87">
-        <v>5.564946085673887</v>
+        <v>6.316629402452278</v>
       </c>
       <c r="U87">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.2128544168548155</v>
+        <v>0.1538032413088569</v>
       </c>
       <c r="W87">
-        <v>0.1155529716057131</v>
+        <v>0.1699163091451815</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.8032242145464736</v>
+        <v>0.5803895898447431</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1908314333025218</v>
+        <v>0.1923814333025218</v>
       </c>
       <c r="C88">
-        <v>-1000.092122260941</v>
+        <v>-1035.692614379666</v>
       </c>
       <c r="D88">
-        <v>1156.223877739058</v>
+        <v>1147.429385620334</v>
       </c>
       <c r="E88">
-        <v>704.3159999999998</v>
+        <v>731.1219999999998</v>
       </c>
       <c r="F88">
-        <v>2305.316</v>
+        <v>2332.122</v>
       </c>
       <c r="G88">
         <v>149</v>
@@ -8497,37 +8497,37 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M88">
-        <v>462.9074528</v>
+        <v>468.2900976</v>
       </c>
       <c r="N88">
-        <v>-194.2407861333332</v>
+        <v>-199.6234309333332</v>
       </c>
       <c r="O88">
-        <v>-51.47380832533332</v>
+        <v>-52.9002091973333</v>
       </c>
       <c r="P88">
-        <v>-142.7669778079999</v>
+        <v>-146.7232217359999</v>
       </c>
       <c r="Q88">
-        <v>180.2330221920001</v>
+        <v>176.2767782640001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3193100531261835</v>
+        <v>0.3403492879820439</v>
       </c>
       <c r="T88">
-        <v>6.316629402452278</v>
+        <v>6.802523971871684</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1538032413088569</v>
+        <v>0.1520353879604792</v>
       </c>
       <c r="W88">
-        <v>0.1699163091451815</v>
+        <v>0.1702712940975358</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5803895898447431</v>
+        <v>0.5737184451338839</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1923814333025218</v>
+        <v>0.1939314333025219</v>
       </c>
       <c r="C89">
-        <v>-1035.692614379666</v>
+        <v>-1071.160330752312</v>
       </c>
       <c r="D89">
-        <v>1147.429385620334</v>
+        <v>1138.767669247688</v>
       </c>
       <c r="E89">
-        <v>731.1219999999998</v>
+        <v>757.9279999999999</v>
       </c>
       <c r="F89">
-        <v>2332.122</v>
+        <v>2358.928</v>
       </c>
       <c r="G89">
         <v>149</v>
@@ -8579,37 +8579,37 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M89">
-        <v>468.2900976</v>
+        <v>473.6727424</v>
       </c>
       <c r="N89">
-        <v>-199.6234309333332</v>
+        <v>-205.0060757333333</v>
       </c>
       <c r="O89">
-        <v>-52.9002091973333</v>
+        <v>-54.32661006933332</v>
       </c>
       <c r="P89">
-        <v>-146.7232217359999</v>
+        <v>-150.6794656639999</v>
       </c>
       <c r="Q89">
-        <v>176.2767782640001</v>
+        <v>172.3205343360001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3403492879820439</v>
+        <v>0.3648950619805476</v>
       </c>
       <c r="T89">
-        <v>6.802523971871684</v>
+        <v>7.369400969527659</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1520353879604792</v>
+        <v>0.150307713097292</v>
       </c>
       <c r="W89">
-        <v>0.1702712940975358</v>
+        <v>0.1706182112100638</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5737184451338839</v>
+        <v>0.5671989173482717</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1939314333025219</v>
+        <v>0.1954814333025218</v>
       </c>
       <c r="C90">
-        <v>-1071.160330752312</v>
+        <v>-1106.498255743655</v>
       </c>
       <c r="D90">
-        <v>1138.767669247688</v>
+        <v>1130.235744256345</v>
       </c>
       <c r="E90">
-        <v>757.9279999999999</v>
+        <v>784.7339999999999</v>
       </c>
       <c r="F90">
-        <v>2358.928</v>
+        <v>2385.734</v>
       </c>
       <c r="G90">
         <v>149</v>
@@ -8661,37 +8661,37 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M90">
-        <v>473.6727424</v>
+        <v>479.0553872</v>
       </c>
       <c r="N90">
-        <v>-205.0060757333333</v>
+        <v>-210.3887205333332</v>
       </c>
       <c r="O90">
-        <v>-54.32661006933332</v>
+        <v>-55.75301094133332</v>
       </c>
       <c r="P90">
-        <v>-150.6794656639999</v>
+        <v>-154.6357095919999</v>
       </c>
       <c r="Q90">
-        <v>172.3205343360001</v>
+        <v>168.3642904080001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3648950619805476</v>
+        <v>0.3939037039787792</v>
       </c>
       <c r="T90">
-        <v>7.369400969527659</v>
+        <v>8.039346512211992</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.150307713097292</v>
+        <v>0.1486188623883337</v>
       </c>
       <c r="W90">
-        <v>0.1706182112100638</v>
+        <v>0.1709573324324226</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5671989173482717</v>
+        <v>0.5608258958050326</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1954814333025218</v>
+        <v>0.1970314333025218</v>
       </c>
       <c r="C91">
-        <v>-1106.498255743655</v>
+        <v>-1141.709284945226</v>
       </c>
       <c r="D91">
-        <v>1130.235744256345</v>
+        <v>1121.830715054774</v>
       </c>
       <c r="E91">
-        <v>784.7339999999999</v>
+        <v>811.54</v>
       </c>
       <c r="F91">
-        <v>2385.734</v>
+        <v>2412.54</v>
       </c>
       <c r="G91">
         <v>149</v>
@@ -8743,37 +8743,37 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M91">
-        <v>479.0553872</v>
+        <v>484.438032</v>
       </c>
       <c r="N91">
-        <v>-210.3887205333332</v>
+        <v>-215.7713653333333</v>
       </c>
       <c r="O91">
-        <v>-55.75301094133332</v>
+        <v>-57.17941181333332</v>
       </c>
       <c r="P91">
-        <v>-154.6357095919999</v>
+        <v>-158.5919535199999</v>
       </c>
       <c r="Q91">
-        <v>168.3642904080001</v>
+        <v>164.4080464800001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3939037039787792</v>
+        <v>0.4287140743766572</v>
       </c>
       <c r="T91">
-        <v>8.039346512211992</v>
+        <v>8.843281163433192</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1486188623883337</v>
+        <v>0.1469675416951299</v>
       </c>
       <c r="W91">
-        <v>0.1709573324324226</v>
+        <v>0.1712889176276179</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5608258958050326</v>
+        <v>0.5545944969627544</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1970314333025218</v>
+        <v>0.1985814333025218</v>
       </c>
       <c r="C92">
-        <v>-1141.709284945226</v>
+        <v>-1176.796228451772</v>
       </c>
       <c r="D92">
-        <v>1121.830715054774</v>
+        <v>1113.549771548228</v>
       </c>
       <c r="E92">
-        <v>811.54</v>
+        <v>838.346</v>
       </c>
       <c r="F92">
-        <v>2412.54</v>
+        <v>2439.346</v>
       </c>
       <c r="G92">
         <v>149</v>
@@ -8825,37 +8825,37 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M92">
-        <v>484.438032</v>
+        <v>489.8206768</v>
       </c>
       <c r="N92">
-        <v>-215.7713653333333</v>
+        <v>-221.1540101333333</v>
       </c>
       <c r="O92">
-        <v>-57.17941181333332</v>
+        <v>-58.60581268533332</v>
       </c>
       <c r="P92">
-        <v>-158.5919535199999</v>
+        <v>-162.5481974479999</v>
       </c>
       <c r="Q92">
-        <v>164.4080464800001</v>
+        <v>160.4518025520001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4287140743766572</v>
+        <v>0.4712600826407301</v>
       </c>
       <c r="T92">
-        <v>8.843281163433192</v>
+        <v>9.825867959370212</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1469675416951299</v>
+        <v>0.1453525137644142</v>
       </c>
       <c r="W92">
-        <v>0.1712889176276179</v>
+        <v>0.1716132152361056</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5545944969627544</v>
+        <v>0.5485000519411858</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1985814333025218</v>
+        <v>0.2001314333025218</v>
       </c>
       <c r="C93">
-        <v>-1176.796228451772</v>
+        <v>-1211.761813993662</v>
       </c>
       <c r="D93">
-        <v>1113.549771548228</v>
+        <v>1105.390186006338</v>
       </c>
       <c r="E93">
-        <v>838.346</v>
+        <v>865.152</v>
       </c>
       <c r="F93">
-        <v>2439.346</v>
+        <v>2466.152</v>
       </c>
       <c r="G93">
         <v>149</v>
@@ -8907,37 +8907,37 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M93">
-        <v>489.8206768</v>
+        <v>495.2033216</v>
       </c>
       <c r="N93">
-        <v>-221.1540101333333</v>
+        <v>-226.5366549333333</v>
       </c>
       <c r="O93">
-        <v>-58.60581268533332</v>
+        <v>-60.03221355733333</v>
       </c>
       <c r="P93">
-        <v>-162.5481974479999</v>
+        <v>-166.504441376</v>
       </c>
       <c r="Q93">
-        <v>160.4518025520001</v>
+        <v>156.495558624</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4712600826407301</v>
+        <v>0.5244425929708215</v>
       </c>
       <c r="T93">
-        <v>9.825867959370212</v>
+        <v>11.05410145429149</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1453525137644142</v>
+        <v>0.1437725951365401</v>
       </c>
       <c r="W93">
-        <v>0.1716132152361056</v>
+        <v>0.1719304628965827</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5485000519411858</v>
+        <v>0.5425380948548684</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2001314333025218</v>
+        <v>0.2016814333025218</v>
       </c>
       <c r="C94">
-        <v>-1211.761813993662</v>
+        <v>-1246.608689932579</v>
       </c>
       <c r="D94">
-        <v>1105.390186006338</v>
+        <v>1097.349310067421</v>
       </c>
       <c r="E94">
-        <v>865.152</v>
+        <v>891.9580000000001</v>
       </c>
       <c r="F94">
-        <v>2466.152</v>
+        <v>2492.958</v>
       </c>
       <c r="G94">
         <v>149</v>
@@ -8989,37 +8989,37 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M94">
-        <v>495.2033216</v>
+        <v>500.5859664</v>
       </c>
       <c r="N94">
-        <v>-226.5366549333333</v>
+        <v>-231.9192997333333</v>
       </c>
       <c r="O94">
-        <v>-60.03221355733333</v>
+        <v>-61.45861442933332</v>
       </c>
       <c r="P94">
-        <v>-166.504441376</v>
+        <v>-170.460685304</v>
       </c>
       <c r="Q94">
-        <v>156.495558624</v>
+        <v>152.539314696</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5244425929708215</v>
+        <v>0.5928201062523675</v>
       </c>
       <c r="T94">
-        <v>11.05410145429149</v>
+        <v>12.63325880490456</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1437725951365401</v>
+        <v>0.1422266532533515</v>
       </c>
       <c r="W94">
-        <v>0.1719304628965827</v>
+        <v>0.172240888026727</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5425380948548684</v>
+        <v>0.5367043518994398</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2016814333025218</v>
+        <v>0.2032314333025219</v>
       </c>
       <c r="C95">
-        <v>-1246.608689932579</v>
+        <v>-1281.33942812741</v>
       </c>
       <c r="D95">
-        <v>1097.349310067421</v>
+        <v>1089.42457187259</v>
       </c>
       <c r="E95">
-        <v>891.9580000000001</v>
+        <v>918.7640000000001</v>
       </c>
       <c r="F95">
-        <v>2492.958</v>
+        <v>2519.764</v>
       </c>
       <c r="G95">
         <v>149</v>
@@ -9071,37 +9071,37 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M95">
-        <v>500.5859664</v>
+        <v>505.9686112000001</v>
       </c>
       <c r="N95">
-        <v>-231.9192997333333</v>
+        <v>-237.3019445333333</v>
       </c>
       <c r="O95">
-        <v>-61.45861442933332</v>
+        <v>-62.88501530133333</v>
       </c>
       <c r="P95">
-        <v>-170.460685304</v>
+        <v>-174.416929232</v>
       </c>
       <c r="Q95">
-        <v>152.539314696</v>
+        <v>148.583070768</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5928201062523675</v>
+        <v>0.6839901239610956</v>
       </c>
       <c r="T95">
-        <v>12.63325880490456</v>
+        <v>14.73880193905533</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1422266532533515</v>
+        <v>0.1407136037506563</v>
       </c>
       <c r="W95">
-        <v>0.172240888026727</v>
+        <v>0.1725447083668682</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5367043518994398</v>
+        <v>0.5309947311345521</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2032314333025219</v>
+        <v>0.2047814333025218</v>
       </c>
       <c r="C96">
-        <v>-1281.33942812741</v>
+        <v>-1315.956526676842</v>
       </c>
       <c r="D96">
-        <v>1089.42457187259</v>
+        <v>1081.613473323159</v>
       </c>
       <c r="E96">
-        <v>918.7640000000001</v>
+        <v>945.5700000000002</v>
       </c>
       <c r="F96">
-        <v>2519.764</v>
+        <v>2546.57</v>
       </c>
       <c r="G96">
         <v>149</v>
@@ -9153,37 +9153,37 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M96">
-        <v>505.9686112000001</v>
+        <v>511.351256</v>
       </c>
       <c r="N96">
-        <v>-237.3019445333333</v>
+        <v>-242.6845893333333</v>
       </c>
       <c r="O96">
-        <v>-62.88501530133333</v>
+        <v>-64.31141617333333</v>
       </c>
       <c r="P96">
-        <v>-174.416929232</v>
+        <v>-178.37317316</v>
       </c>
       <c r="Q96">
-        <v>148.583070768</v>
+        <v>144.62682684</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6839901239610956</v>
+        <v>0.8116281487533151</v>
       </c>
       <c r="T96">
-        <v>14.73880193905533</v>
+        <v>17.6865623268664</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1407136037506563</v>
+        <v>0.1392324079217021</v>
       </c>
       <c r="W96">
-        <v>0.1725447083668682</v>
+        <v>0.1728421324893222</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5309947311345521</v>
+        <v>0.5254053129120831</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2047814333025218</v>
+        <v>0.2063314333025218</v>
       </c>
       <c r="C97">
-        <v>-1315.956526676842</v>
+        <v>-1350.462412544817</v>
       </c>
       <c r="D97">
-        <v>1081.613473323159</v>
+        <v>1073.913587455184</v>
       </c>
       <c r="E97">
-        <v>945.5700000000002</v>
+        <v>972.3760000000002</v>
       </c>
       <c r="F97">
-        <v>2546.57</v>
+        <v>2573.376</v>
       </c>
       <c r="G97">
         <v>149</v>
@@ -9235,37 +9235,37 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M97">
-        <v>511.351256</v>
+        <v>516.7339008</v>
       </c>
       <c r="N97">
-        <v>-242.6845893333333</v>
+        <v>-248.0672341333333</v>
       </c>
       <c r="O97">
-        <v>-64.31141617333333</v>
+        <v>-65.73781704533332</v>
       </c>
       <c r="P97">
-        <v>-178.37317316</v>
+        <v>-182.329417088</v>
       </c>
       <c r="Q97">
-        <v>144.62682684</v>
+        <v>140.670582912</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8116281487533151</v>
+        <v>1.003085185941644</v>
       </c>
       <c r="T97">
-        <v>17.6865623268664</v>
+        <v>22.10820290858301</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1392324079217021</v>
+        <v>0.1377820703391843</v>
       </c>
       <c r="W97">
-        <v>0.1728421324893222</v>
+        <v>0.1731333602758918</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5254053129120831</v>
+        <v>0.5199323409025822</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2063314333025218</v>
+        <v>0.2078814333025218</v>
       </c>
       <c r="C98">
-        <v>-1350.462412544816</v>
+        <v>-1384.859444074634</v>
       </c>
       <c r="D98">
-        <v>1073.913587455184</v>
+        <v>1066.322555925365</v>
       </c>
       <c r="E98">
-        <v>972.3759999999997</v>
+        <v>999.1819999999998</v>
       </c>
       <c r="F98">
-        <v>2573.376</v>
+        <v>2600.182</v>
       </c>
       <c r="G98">
         <v>149</v>
@@ -9317,37 +9317,37 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M98">
-        <v>516.7339008</v>
+        <v>522.1165456</v>
       </c>
       <c r="N98">
-        <v>-248.0672341333333</v>
+        <v>-253.4498789333333</v>
       </c>
       <c r="O98">
-        <v>-65.73781704533332</v>
+        <v>-67.16421791733332</v>
       </c>
       <c r="P98">
-        <v>-182.329417088</v>
+        <v>-186.2856610159999</v>
       </c>
       <c r="Q98">
-        <v>140.670582912</v>
+        <v>136.7143389840001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.003085185941642</v>
+        <v>1.322180247922189</v>
       </c>
       <c r="T98">
-        <v>22.10820290858296</v>
+        <v>29.47760387811061</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1377820703391843</v>
+        <v>0.1363616366243474</v>
       </c>
       <c r="W98">
-        <v>0.1731333602758918</v>
+        <v>0.173418583365831</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5199323409025822</v>
+        <v>0.5145722136767825</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2078814333025218</v>
+        <v>0.2094314333025218</v>
       </c>
       <c r="C99">
-        <v>-1384.859444074634</v>
+        <v>-1419.149913397181</v>
       </c>
       <c r="D99">
-        <v>1066.322555925365</v>
+        <v>1058.838086602819</v>
       </c>
       <c r="E99">
-        <v>999.1819999999998</v>
+        <v>1025.988</v>
       </c>
       <c r="F99">
-        <v>2600.182</v>
+        <v>2626.988</v>
       </c>
       <c r="G99">
         <v>149</v>
@@ -9399,37 +9399,37 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M99">
-        <v>522.1165456</v>
+        <v>527.4991904</v>
       </c>
       <c r="N99">
-        <v>-253.4498789333333</v>
+        <v>-258.8325237333332</v>
       </c>
       <c r="O99">
-        <v>-67.16421791733332</v>
+        <v>-68.59061878933331</v>
       </c>
       <c r="P99">
-        <v>-186.2856610159999</v>
+        <v>-190.2419049439999</v>
       </c>
       <c r="Q99">
-        <v>136.7143389840001</v>
+        <v>132.7580950560001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.322180247922189</v>
+        <v>1.960370371883283</v>
       </c>
       <c r="T99">
-        <v>29.47760387811061</v>
+        <v>44.21640581716591</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1363616366243474</v>
+        <v>0.1349701913526704</v>
       </c>
       <c r="W99">
-        <v>0.173418583365831</v>
+        <v>0.1736979855763838</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5145722136767825</v>
+        <v>0.5093214768025296</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2094314333025218</v>
+        <v>0.2109814333025218</v>
       </c>
       <c r="C100">
-        <v>-1419.149913397181</v>
+        <v>-1453.336048738439</v>
       </c>
       <c r="D100">
-        <v>1058.838086602819</v>
+        <v>1051.457951261561</v>
       </c>
       <c r="E100">
-        <v>1025.988</v>
+        <v>1052.794</v>
       </c>
       <c r="F100">
-        <v>2626.988</v>
+        <v>2653.794</v>
       </c>
       <c r="G100">
         <v>149</v>
@@ -9481,37 +9481,37 @@
         <v>268.6666666666667</v>
       </c>
       <c r="M100">
-        <v>527.4991904</v>
+        <v>532.8818352</v>
       </c>
       <c r="N100">
-        <v>-258.8325237333332</v>
+        <v>-264.2151685333332</v>
       </c>
       <c r="O100">
-        <v>-68.59061878933331</v>
+        <v>-70.01701966133331</v>
       </c>
       <c r="P100">
-        <v>-190.2419049439999</v>
+        <v>-194.1981488719999</v>
       </c>
       <c r="Q100">
-        <v>132.7580950560001</v>
+        <v>128.8018511280001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.960370371883283</v>
+        <v>3.874940743766567</v>
       </c>
       <c r="T100">
-        <v>44.21640581716591</v>
+        <v>88.43281163433181</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1349701913526704</v>
+        <v>0.1336068560864818</v>
       </c>
       <c r="W100">
-        <v>0.1736979855763838</v>
+        <v>0.1739717432978345</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5093214768025296</v>
+        <v>0.5041768154206859</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2109814333025218</v>
-      </c>
-      <c r="C101">
-        <v>-1453.336048738439</v>
-      </c>
-      <c r="D101">
-        <v>1051.457951261561</v>
-      </c>
-      <c r="E101">
-        <v>1052.794</v>
-      </c>
-      <c r="F101">
-        <v>2653.794</v>
-      </c>
-      <c r="G101">
-        <v>149</v>
-      </c>
-      <c r="H101">
-        <v>1079.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>591.6666666666667</v>
-      </c>
-      <c r="K101">
-        <v>323</v>
-      </c>
-      <c r="L101">
-        <v>268.6666666666667</v>
-      </c>
-      <c r="M101">
-        <v>532.8818352</v>
-      </c>
-      <c r="N101">
-        <v>-264.2151685333332</v>
-      </c>
-      <c r="O101">
-        <v>-70.01701966133331</v>
-      </c>
-      <c r="P101">
-        <v>-194.1981488719999</v>
-      </c>
-      <c r="Q101">
-        <v>128.8018511280001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.874940743766567</v>
-      </c>
-      <c r="T101">
-        <v>88.43281163433181</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1336068560864818</v>
-      </c>
-      <c r="W101">
-        <v>0.1739717432978345</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5041768154206859</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
